--- a/xlsx/BWV.xlsx
+++ b/xlsx/BWV.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Parker\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Parker\WebstormProjects\konzert-public-data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9805"/>
+    <workbookView windowWidth="21094" windowHeight="9805"/>
   </bookViews>
   <sheets>
     <sheet name="BWV" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BWV!$A$1:$G$588</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BWV!$A$1:$G$723</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$G$408</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3502" uniqueCount="1523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3565" uniqueCount="1524">
   <si>
     <t>Catalogue</t>
   </si>
@@ -5288,7 +5288,16 @@
     <t>2 Harpsichords, 2 Violins, Viola, Basso Continuo</t>
   </si>
   <si>
-    <t>Récupération d'un concerto perdu pour 2 Violins ou Oboes, Violin</t>
+    <t>Based on a lost concerto, possibly for oboe and violin or two violins</t>
+  </si>
+  <si>
+    <t>BWV 1060R</t>
+  </si>
+  <si>
+    <t>Solo Oboe, Solo Violin, 2 Violins, Viola, Basso Continuo</t>
+  </si>
+  <si>
+    <t>Reconstruction of the lost original concerto</t>
   </si>
   <si>
     <t>BWV 1061</t>
@@ -5664,12 +5673,6 @@
   </si>
   <si>
     <t>BWV 1090</t>
-  </si>
-  <si>
-    <t>BWV 1090-1120</t>
-  </si>
-  <si>
-    <t>Préludes de chorals pour orgue</t>
   </si>
   <si>
     <t>Manuscrit Johann Gottfried Neumeister - Yale University</t>
@@ -7310,7 +7313,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="1" spans="1:7">
+    <row r="3" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A3" s="13" t="s">
         <v>13</v>
       </c>
@@ -7331,7 +7334,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" spans="1:7">
+    <row r="4" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A4" s="13" t="s">
         <v>18</v>
       </c>
@@ -7352,7 +7355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" spans="1:7">
+    <row r="5" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A5" s="13" t="s">
         <v>23</v>
       </c>
@@ -7373,7 +7376,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" s="8" customFormat="1" spans="1:7">
+    <row r="6" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A6" s="13" t="s">
         <v>28</v>
       </c>
@@ -7394,7 +7397,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" s="8" customFormat="1" spans="1:7">
+    <row r="7" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A7" s="13" t="s">
         <v>33</v>
       </c>
@@ -7415,7 +7418,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="1" spans="1:7">
+    <row r="8" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A8" s="13" t="s">
         <v>38</v>
       </c>
@@ -7436,7 +7439,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" s="9" customFormat="1" spans="1:7">
+    <row r="9" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A9" s="13" t="s">
         <v>43</v>
       </c>
@@ -7457,7 +7460,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" s="9" customFormat="1" spans="1:7">
+    <row r="10" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A10" s="13" t="s">
         <v>48</v>
       </c>
@@ -7499,7 +7502,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="1" spans="1:7">
+    <row r="12" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A12" s="13" t="s">
         <v>57</v>
       </c>
@@ -7520,7 +7523,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" s="8" customFormat="1" spans="1:7">
+    <row r="13" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A13" s="13" t="s">
         <v>62</v>
       </c>
@@ -7541,7 +7544,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" s="8" customFormat="1" spans="1:7">
+    <row r="14" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A14" s="13" t="s">
         <v>67</v>
       </c>
@@ -7562,7 +7565,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" s="8" customFormat="1" spans="1:7">
+    <row r="15" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A15" s="13" t="s">
         <v>72</v>
       </c>
@@ -7583,7 +7586,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" s="8" customFormat="1" spans="1:7">
+    <row r="16" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A16" s="13" t="s">
         <v>77</v>
       </c>
@@ -7604,7 +7607,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" s="8" customFormat="1" spans="1:7">
+    <row r="17" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A17" s="13" t="s">
         <v>82</v>
       </c>
@@ -7625,7 +7628,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" s="8" customFormat="1" spans="1:7">
+    <row r="18" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A18" s="13" t="s">
         <v>87</v>
       </c>
@@ -7646,7 +7649,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" s="8" customFormat="1" spans="1:7">
+    <row r="19" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A19" s="13" t="s">
         <v>92</v>
       </c>
@@ -7667,7 +7670,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" s="8" customFormat="1" spans="1:7">
+    <row r="20" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A20" s="13" t="s">
         <v>97</v>
       </c>
@@ -7688,7 +7691,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" s="8" customFormat="1" spans="1:7">
+    <row r="21" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A21" s="13" t="s">
         <v>102</v>
       </c>
@@ -7709,7 +7712,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" s="8" customFormat="1" spans="1:7">
+    <row r="22" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A22" s="15" t="s">
         <v>107</v>
       </c>
@@ -7728,7 +7731,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" s="8" customFormat="1" spans="1:7">
+    <row r="23" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A23" s="15" t="s">
         <v>111</v>
       </c>
@@ -7747,7 +7750,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" s="8" customFormat="1" spans="1:7">
+    <row r="24" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A24" s="15" t="s">
         <v>115</v>
       </c>
@@ -7766,7 +7769,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" s="8" customFormat="1" spans="1:7">
+    <row r="25" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A25" s="15" t="s">
         <v>119</v>
       </c>
@@ -7785,7 +7788,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" s="8" customFormat="1" spans="1:7">
+    <row r="26" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A26" s="15" t="s">
         <v>123</v>
       </c>
@@ -7804,7 +7807,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" s="8" customFormat="1" spans="1:7">
+    <row r="27" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A27" s="15" t="s">
         <v>127</v>
       </c>
@@ -7823,7 +7826,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" s="8" customFormat="1" spans="1:7">
+    <row r="28" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A28" s="15" t="s">
         <v>131</v>
       </c>
@@ -7840,7 +7843,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="29" s="8" customFormat="1" spans="1:7">
+    <row r="29" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A29" s="15" t="s">
         <v>134</v>
       </c>
@@ -7857,7 +7860,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="30" s="8" customFormat="1" spans="1:7">
+    <row r="30" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A30" s="15" t="s">
         <v>137</v>
       </c>
@@ -7874,7 +7877,7 @@
       </c>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" s="8" customFormat="1" spans="1:7">
+    <row r="31" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A31" s="13" t="s">
         <v>141</v>
       </c>
@@ -7891,7 +7894,7 @@
       </c>
       <c r="G31" s="14"/>
     </row>
-    <row r="32" s="8" customFormat="1" spans="1:7">
+    <row r="32" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A32" s="15" t="s">
         <v>144</v>
       </c>
@@ -7910,7 +7913,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" s="8" customFormat="1" spans="1:7">
+    <row r="33" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A33" s="15" t="s">
         <v>148</v>
       </c>
@@ -7927,7 +7930,7 @@
       </c>
       <c r="G33" s="14"/>
     </row>
-    <row r="34" s="8" customFormat="1" spans="1:7">
+    <row r="34" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A34" s="17" t="s">
         <v>151</v>
       </c>
@@ -7944,7 +7947,7 @@
       </c>
       <c r="G34" s="14"/>
     </row>
-    <row r="35" s="8" customFormat="1" spans="1:7">
+    <row r="35" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A35" s="17" t="s">
         <v>154</v>
       </c>
@@ -7961,7 +7964,7 @@
       </c>
       <c r="G35" s="14"/>
     </row>
-    <row r="36" s="8" customFormat="1" spans="1:7">
+    <row r="36" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A36" s="17" t="s">
         <v>157</v>
       </c>
@@ -7980,7 +7983,7 @@
       </c>
       <c r="G36" s="14"/>
     </row>
-    <row r="37" s="8" customFormat="1" spans="1:7">
+    <row r="37" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A37" s="17" t="s">
         <v>161</v>
       </c>
@@ -7999,7 +8002,7 @@
       </c>
       <c r="G37" s="14"/>
     </row>
-    <row r="38" s="8" customFormat="1" spans="1:7">
+    <row r="38" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A38" s="17" t="s">
         <v>164</v>
       </c>
@@ -8018,7 +8021,7 @@
       </c>
       <c r="G38" s="14"/>
     </row>
-    <row r="39" s="8" customFormat="1" spans="1:7">
+    <row r="39" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A39" s="17" t="s">
         <v>167</v>
       </c>
@@ -8037,7 +8040,7 @@
       </c>
       <c r="G39" s="14"/>
     </row>
-    <row r="40" s="8" customFormat="1" spans="1:7">
+    <row r="40" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A40" s="17" t="s">
         <v>169</v>
       </c>
@@ -8056,7 +8059,7 @@
       </c>
       <c r="G40" s="14"/>
     </row>
-    <row r="41" s="8" customFormat="1" spans="1:7">
+    <row r="41" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A41" s="17" t="s">
         <v>171</v>
       </c>
@@ -8075,7 +8078,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="42" s="8" customFormat="1" spans="1:7">
+    <row r="42" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A42" s="15" t="s">
         <v>174</v>
       </c>
@@ -8092,7 +8095,7 @@
       </c>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" s="8" customFormat="1" spans="1:7">
+    <row r="43" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A43" s="13" t="s">
         <v>178</v>
       </c>
@@ -8109,7 +8112,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="44" s="8" customFormat="1" spans="1:7">
+    <row r="44" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A44" s="13" t="s">
         <v>182</v>
       </c>
@@ -8130,7 +8133,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="45" s="8" customFormat="1" spans="1:7">
+    <row r="45" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A45" s="15" t="s">
         <v>188</v>
       </c>
@@ -8147,7 +8150,7 @@
       </c>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" s="8" customFormat="1" spans="1:7">
+    <row r="46" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A46" s="15" t="s">
         <v>191</v>
       </c>
@@ -8170,7 +8173,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" s="8" customFormat="1" spans="1:7">
+    <row r="47" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A47" s="15" t="s">
         <v>198</v>
       </c>
@@ -8193,7 +8196,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="48" s="8" customFormat="1" spans="1:7">
+    <row r="48" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A48" s="15" t="s">
         <v>203</v>
       </c>
@@ -8216,7 +8219,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="49" s="8" customFormat="1" spans="1:7">
+    <row r="49" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A49" s="15" t="s">
         <v>209</v>
       </c>
@@ -8231,7 +8234,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" s="8" customFormat="1" spans="1:7">
+    <row r="50" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A50" s="15" t="s">
         <v>211</v>
       </c>
@@ -8250,7 +8253,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="51" s="8" customFormat="1" spans="1:7">
+    <row r="51" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A51" s="13" t="s">
         <v>215</v>
       </c>
@@ -8269,7 +8272,7 @@
       </c>
       <c r="G51" s="14"/>
     </row>
-    <row r="52" s="8" customFormat="1" spans="1:7">
+    <row r="52" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A52" s="13" t="s">
         <v>220</v>
       </c>
@@ -8288,7 +8291,7 @@
       </c>
       <c r="G52" s="14"/>
     </row>
-    <row r="53" s="8" customFormat="1" spans="1:7">
+    <row r="53" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A53" s="13" t="s">
         <v>222</v>
       </c>
@@ -8307,7 +8310,7 @@
       </c>
       <c r="G53" s="14"/>
     </row>
-    <row r="54" s="8" customFormat="1" spans="1:7">
+    <row r="54" s="8" customFormat="1" ht="15.45" spans="1:7">
       <c r="A54" s="13" t="s">
         <v>224</v>
       </c>
@@ -8326,7 +8329,7 @@
       </c>
       <c r="G54" s="14"/>
     </row>
-    <row r="55" s="8" customFormat="1" spans="1:7">
+    <row r="55" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A55" s="13" t="s">
         <v>227</v>
       </c>
@@ -8345,7 +8348,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="56" s="8" customFormat="1" spans="1:7">
+    <row r="56" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A56" s="13" t="s">
         <v>230</v>
       </c>
@@ -8364,7 +8367,7 @@
       </c>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" s="8" customFormat="1" spans="1:7">
+    <row r="57" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A57" s="13" t="s">
         <v>232</v>
       </c>
@@ -8383,7 +8386,7 @@
       </c>
       <c r="G57" s="14"/>
     </row>
-    <row r="58" s="8" customFormat="1" spans="1:7">
+    <row r="58" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A58" s="13" t="s">
         <v>234</v>
       </c>
@@ -8400,7 +8403,7 @@
       </c>
       <c r="G58" s="14"/>
     </row>
-    <row r="59" s="8" customFormat="1" spans="1:7">
+    <row r="59" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A59" s="13" t="s">
         <v>236</v>
       </c>
@@ -8417,7 +8420,7 @@
       </c>
       <c r="G59" s="14"/>
     </row>
-    <row r="60" s="8" customFormat="1" spans="1:7">
+    <row r="60" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A60" s="13" t="s">
         <v>237</v>
       </c>
@@ -8436,7 +8439,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="61" s="8" customFormat="1" spans="1:7">
+    <row r="61" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A61" s="13" t="s">
         <v>240</v>
       </c>
@@ -8453,7 +8456,7 @@
       </c>
       <c r="G61" s="14"/>
     </row>
-    <row r="62" s="8" customFormat="1" spans="1:7">
+    <row r="62" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A62" s="13" t="s">
         <v>242</v>
       </c>
@@ -8470,7 +8473,7 @@
       </c>
       <c r="G62" s="14"/>
     </row>
-    <row r="63" s="8" customFormat="1" spans="1:7">
+    <row r="63" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A63" s="13" t="s">
         <v>244</v>
       </c>
@@ -8487,7 +8490,7 @@
       </c>
       <c r="G63" s="14"/>
     </row>
-    <row r="64" s="8" customFormat="1" spans="1:7">
+    <row r="64" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A64" s="13" t="s">
         <v>245</v>
       </c>
@@ -8506,7 +8509,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="65" s="8" customFormat="1" spans="1:7">
+    <row r="65" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A65" s="13" t="s">
         <v>247</v>
       </c>
@@ -8523,7 +8526,7 @@
       </c>
       <c r="G65" s="14"/>
     </row>
-    <row r="66" s="8" customFormat="1" spans="1:7">
+    <row r="66" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A66" s="13" t="s">
         <v>248</v>
       </c>
@@ -8542,7 +8545,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="67" s="8" customFormat="1" spans="1:7">
+    <row r="67" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A67" s="13" t="s">
         <v>250</v>
       </c>
@@ -8559,7 +8562,7 @@
       </c>
       <c r="G67" s="14"/>
     </row>
-    <row r="68" s="8" customFormat="1" spans="1:7">
+    <row r="68" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A68" s="13" t="s">
         <v>252</v>
       </c>
@@ -8576,7 +8579,7 @@
       </c>
       <c r="G68" s="14"/>
     </row>
-    <row r="69" s="8" customFormat="1" spans="1:7">
+    <row r="69" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A69" s="13" t="s">
         <v>254</v>
       </c>
@@ -8593,7 +8596,7 @@
       </c>
       <c r="G69" s="14"/>
     </row>
-    <row r="70" s="8" customFormat="1" spans="1:7">
+    <row r="70" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A70" s="13" t="s">
         <v>255</v>
       </c>
@@ -8612,7 +8615,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="71" s="8" customFormat="1" spans="1:7">
+    <row r="71" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A71" s="13" t="s">
         <v>257</v>
       </c>
@@ -8629,7 +8632,7 @@
       </c>
       <c r="G71" s="14"/>
     </row>
-    <row r="72" s="8" customFormat="1" spans="1:7">
+    <row r="72" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A72" s="13" t="s">
         <v>259</v>
       </c>
@@ -8646,7 +8649,7 @@
       </c>
       <c r="G72" s="14"/>
     </row>
-    <row r="73" s="8" customFormat="1" spans="1:7">
+    <row r="73" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A73" s="13" t="s">
         <v>260</v>
       </c>
@@ -8663,7 +8666,7 @@
       </c>
       <c r="G73" s="14"/>
     </row>
-    <row r="74" s="8" customFormat="1" spans="1:7">
+    <row r="74" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A74" s="13" t="s">
         <v>262</v>
       </c>
@@ -8682,7 +8685,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="75" s="8" customFormat="1" spans="1:7">
+    <row r="75" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A75" s="13" t="s">
         <v>264</v>
       </c>
@@ -8699,7 +8702,7 @@
       </c>
       <c r="G75" s="14"/>
     </row>
-    <row r="76" s="8" customFormat="1" spans="1:7">
+    <row r="76" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A76" s="13" t="s">
         <v>266</v>
       </c>
@@ -8716,7 +8719,7 @@
       </c>
       <c r="G76" s="14"/>
     </row>
-    <row r="77" s="8" customFormat="1" spans="1:7">
+    <row r="77" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A77" s="13" t="s">
         <v>267</v>
       </c>
@@ -8733,7 +8736,7 @@
       </c>
       <c r="G77" s="14"/>
     </row>
-    <row r="78" s="8" customFormat="1" spans="1:7">
+    <row r="78" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A78" s="13" t="s">
         <v>268</v>
       </c>
@@ -8752,7 +8755,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" s="8" customFormat="1" spans="1:7">
+    <row r="79" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A79" s="13" t="s">
         <v>271</v>
       </c>
@@ -8769,7 +8772,7 @@
       </c>
       <c r="G79" s="14"/>
     </row>
-    <row r="80" s="8" customFormat="1" spans="1:7">
+    <row r="80" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A80" s="13" t="s">
         <v>272</v>
       </c>
@@ -8786,7 +8789,7 @@
       </c>
       <c r="G80" s="14"/>
     </row>
-    <row r="81" s="8" customFormat="1" spans="1:7">
+    <row r="81" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A81" s="13" t="s">
         <v>273</v>
       </c>
@@ -8803,7 +8806,7 @@
       </c>
       <c r="G81" s="14"/>
     </row>
-    <row r="82" s="8" customFormat="1" spans="1:7">
+    <row r="82" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A82" s="13" t="s">
         <v>275</v>
       </c>
@@ -8820,7 +8823,7 @@
       </c>
       <c r="G82" s="14"/>
     </row>
-    <row r="83" s="8" customFormat="1" spans="1:7">
+    <row r="83" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A83" s="13" t="s">
         <v>276</v>
       </c>
@@ -8837,7 +8840,7 @@
       </c>
       <c r="G83" s="14"/>
     </row>
-    <row r="84" s="8" customFormat="1" spans="1:7">
+    <row r="84" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A84" s="13" t="s">
         <v>277</v>
       </c>
@@ -8854,7 +8857,7 @@
       </c>
       <c r="G84" s="14"/>
     </row>
-    <row r="85" s="8" customFormat="1" spans="1:7">
+    <row r="85" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A85" s="13" t="s">
         <v>278</v>
       </c>
@@ -8873,7 +8876,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="86" s="8" customFormat="1" spans="1:7">
+    <row r="86" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A86" s="13" t="s">
         <v>281</v>
       </c>
@@ -8890,7 +8893,7 @@
       </c>
       <c r="G86" s="14"/>
     </row>
-    <row r="87" s="8" customFormat="1" spans="1:7">
+    <row r="87" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A87" s="13" t="s">
         <v>283</v>
       </c>
@@ -8907,7 +8910,7 @@
       </c>
       <c r="G87" s="14"/>
     </row>
-    <row r="88" s="8" customFormat="1" spans="1:7">
+    <row r="88" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A88" s="13" t="s">
         <v>284</v>
       </c>
@@ -8924,7 +8927,7 @@
       </c>
       <c r="G88" s="14"/>
     </row>
-    <row r="89" s="8" customFormat="1" spans="1:7">
+    <row r="89" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A89" s="13" t="s">
         <v>285</v>
       </c>
@@ -8941,7 +8944,7 @@
       </c>
       <c r="G89" s="14"/>
     </row>
-    <row r="90" s="8" customFormat="1" spans="1:7">
+    <row r="90" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A90" s="13" t="s">
         <v>286</v>
       </c>
@@ -8958,7 +8961,7 @@
       </c>
       <c r="G90" s="14"/>
     </row>
-    <row r="91" s="8" customFormat="1" spans="1:7">
+    <row r="91" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A91" s="13" t="s">
         <v>287</v>
       </c>
@@ -8975,7 +8978,7 @@
       </c>
       <c r="G91" s="14"/>
     </row>
-    <row r="92" s="8" customFormat="1" spans="1:7">
+    <row r="92" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A92" s="13" t="s">
         <v>288</v>
       </c>
@@ -8992,7 +8995,7 @@
       </c>
       <c r="G92" s="14"/>
     </row>
-    <row r="93" s="8" customFormat="1" spans="1:7">
+    <row r="93" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A93" s="13" t="s">
         <v>289</v>
       </c>
@@ -9007,7 +9010,7 @@
       <c r="F93" s="14"/>
       <c r="G93" s="14"/>
     </row>
-    <row r="94" s="8" customFormat="1" spans="1:7">
+    <row r="94" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A94" s="13" t="s">
         <v>291</v>
       </c>
@@ -9024,7 +9027,7 @@
       </c>
       <c r="G94" s="14"/>
     </row>
-    <row r="95" s="8" customFormat="1" spans="1:7">
+    <row r="95" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A95" s="13" t="s">
         <v>293</v>
       </c>
@@ -9043,7 +9046,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="96" s="8" customFormat="1" spans="1:7">
+    <row r="96" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A96" s="13" t="s">
         <v>295</v>
       </c>
@@ -9062,7 +9065,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="97" s="8" customFormat="1" spans="1:7">
+    <row r="97" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A97" s="13" t="s">
         <v>297</v>
       </c>
@@ -9079,7 +9082,7 @@
       </c>
       <c r="G97" s="14"/>
     </row>
-    <row r="98" s="8" customFormat="1" spans="1:7">
+    <row r="98" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A98" s="13" t="s">
         <v>299</v>
       </c>
@@ -9096,7 +9099,7 @@
       </c>
       <c r="G98" s="14"/>
     </row>
-    <row r="99" s="8" customFormat="1" spans="1:7">
+    <row r="99" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A99" s="13" t="s">
         <v>301</v>
       </c>
@@ -9113,7 +9116,7 @@
       </c>
       <c r="G99" s="14"/>
     </row>
-    <row r="100" s="8" customFormat="1" spans="1:7">
+    <row r="100" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A100" s="13" t="s">
         <v>303</v>
       </c>
@@ -9132,7 +9135,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="101" s="8" customFormat="1" spans="1:7">
+    <row r="101" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A101" s="13" t="s">
         <v>306</v>
       </c>
@@ -9149,7 +9152,7 @@
       </c>
       <c r="G101" s="14"/>
     </row>
-    <row r="102" s="8" customFormat="1" spans="1:7">
+    <row r="102" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A102" s="13" t="s">
         <v>307</v>
       </c>
@@ -9166,7 +9169,7 @@
       </c>
       <c r="G102" s="14"/>
     </row>
-    <row r="103" s="8" customFormat="1" spans="1:7">
+    <row r="103" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A103" s="13" t="s">
         <v>308</v>
       </c>
@@ -9183,7 +9186,7 @@
       </c>
       <c r="G103" s="14"/>
     </row>
-    <row r="104" s="8" customFormat="1" spans="1:7">
+    <row r="104" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A104" s="13" t="s">
         <v>309</v>
       </c>
@@ -9200,7 +9203,7 @@
       </c>
       <c r="G104" s="14"/>
     </row>
-    <row r="105" s="8" customFormat="1" spans="1:7">
+    <row r="105" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A105" s="13" t="s">
         <v>310</v>
       </c>
@@ -9219,7 +9222,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="106" s="8" customFormat="1" spans="1:7">
+    <row r="106" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A106" s="13" t="s">
         <v>312</v>
       </c>
@@ -9236,7 +9239,7 @@
       </c>
       <c r="G106" s="14"/>
     </row>
-    <row r="107" s="8" customFormat="1" spans="1:7">
+    <row r="107" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A107" s="13" t="s">
         <v>313</v>
       </c>
@@ -9255,7 +9258,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="108" s="8" customFormat="1" spans="1:7">
+    <row r="108" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A108" s="13" t="s">
         <v>315</v>
       </c>
@@ -9274,7 +9277,7 @@
       </c>
       <c r="G108" s="14"/>
     </row>
-    <row r="109" s="8" customFormat="1" spans="1:7">
+    <row r="109" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A109" s="13" t="s">
         <v>317</v>
       </c>
@@ -9293,7 +9296,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="110" s="8" customFormat="1" spans="1:7">
+    <row r="110" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A110" s="13" t="s">
         <v>319</v>
       </c>
@@ -9310,7 +9313,7 @@
       </c>
       <c r="G110" s="14"/>
     </row>
-    <row r="111" s="8" customFormat="1" spans="1:7">
+    <row r="111" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A111" s="13" t="s">
         <v>320</v>
       </c>
@@ -9327,7 +9330,7 @@
       </c>
       <c r="G111" s="14"/>
     </row>
-    <row r="112" s="8" customFormat="1" spans="1:7">
+    <row r="112" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A112" s="13" t="s">
         <v>321</v>
       </c>
@@ -9346,7 +9349,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="113" s="8" customFormat="1" spans="1:7">
+    <row r="113" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A113" s="13" t="s">
         <v>323</v>
       </c>
@@ -9365,7 +9368,7 @@
       </c>
       <c r="G113" s="14"/>
     </row>
-    <row r="114" s="8" customFormat="1" spans="1:7">
+    <row r="114" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A114" s="13" t="s">
         <v>325</v>
       </c>
@@ -9386,7 +9389,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="115" s="8" customFormat="1" spans="1:7">
+    <row r="115" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A115" s="13" t="s">
         <v>328</v>
       </c>
@@ -9403,7 +9406,7 @@
       </c>
       <c r="G115" s="14"/>
     </row>
-    <row r="116" s="8" customFormat="1" spans="1:7">
+    <row r="116" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A116" s="13" t="s">
         <v>329</v>
       </c>
@@ -9420,7 +9423,7 @@
       </c>
       <c r="G116" s="14"/>
     </row>
-    <row r="117" s="8" customFormat="1" spans="1:7">
+    <row r="117" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A117" s="13" t="s">
         <v>330</v>
       </c>
@@ -9439,7 +9442,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="118" s="8" customFormat="1" spans="1:7">
+    <row r="118" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A118" s="13" t="s">
         <v>332</v>
       </c>
@@ -9456,7 +9459,7 @@
       </c>
       <c r="G118" s="14"/>
     </row>
-    <row r="119" s="8" customFormat="1" spans="1:7">
+    <row r="119" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A119" s="13" t="s">
         <v>334</v>
       </c>
@@ -9475,7 +9478,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="120" s="8" customFormat="1" spans="1:7">
+    <row r="120" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A120" s="13" t="s">
         <v>336</v>
       </c>
@@ -9494,7 +9497,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="121" s="8" customFormat="1" spans="1:7">
+    <row r="121" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A121" s="13" t="s">
         <v>338</v>
       </c>
@@ -9513,7 +9516,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="122" s="8" customFormat="1" spans="1:7">
+    <row r="122" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A122" s="13" t="s">
         <v>340</v>
       </c>
@@ -9532,7 +9535,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="123" s="8" customFormat="1" spans="1:7">
+    <row r="123" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A123" s="13" t="s">
         <v>342</v>
       </c>
@@ -9551,7 +9554,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="124" s="8" customFormat="1" spans="1:7">
+    <row r="124" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A124" s="13" t="s">
         <v>344</v>
       </c>
@@ -9570,7 +9573,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="125" s="8" customFormat="1" spans="1:7">
+    <row r="125" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A125" s="13" t="s">
         <v>346</v>
       </c>
@@ -9585,7 +9588,7 @@
       <c r="F125" s="14"/>
       <c r="G125" s="14"/>
     </row>
-    <row r="126" s="8" customFormat="1" spans="1:7">
+    <row r="126" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A126" s="13" t="s">
         <v>348</v>
       </c>
@@ -9602,7 +9605,7 @@
       </c>
       <c r="G126" s="14"/>
     </row>
-    <row r="127" s="8" customFormat="1" spans="1:7">
+    <row r="127" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A127" s="13" t="s">
         <v>350</v>
       </c>
@@ -9619,7 +9622,7 @@
       </c>
       <c r="G127" s="14"/>
     </row>
-    <row r="128" s="8" customFormat="1" spans="1:7">
+    <row r="128" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A128" s="13" t="s">
         <v>352</v>
       </c>
@@ -9636,7 +9639,7 @@
       </c>
       <c r="G128" s="14"/>
     </row>
-    <row r="129" s="8" customFormat="1" spans="1:7">
+    <row r="129" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A129" s="13" t="s">
         <v>354</v>
       </c>
@@ -9657,7 +9660,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="130" s="8" customFormat="1" spans="1:7">
+    <row r="130" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A130" s="13" t="s">
         <v>358</v>
       </c>
@@ -9678,7 +9681,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="131" s="8" customFormat="1" spans="1:7">
+    <row r="131" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A131" s="13" t="s">
         <v>360</v>
       </c>
@@ -9699,7 +9702,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="132" s="8" customFormat="1" spans="1:7">
+    <row r="132" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A132" s="13" t="s">
         <v>363</v>
       </c>
@@ -9720,7 +9723,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="133" s="8" customFormat="1" spans="1:7">
+    <row r="133" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A133" s="13" t="s">
         <v>366</v>
       </c>
@@ -9739,7 +9742,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="134" s="8" customFormat="1" spans="1:7">
+    <row r="134" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A134" s="13" t="s">
         <v>368</v>
       </c>
@@ -9760,7 +9763,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="135" s="8" customFormat="1" spans="1:7">
+    <row r="135" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A135" s="13" t="s">
         <v>371</v>
       </c>
@@ -9781,7 +9784,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="136" s="8" customFormat="1" spans="1:7">
+    <row r="136" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A136" s="13" t="s">
         <v>374</v>
       </c>
@@ -9800,7 +9803,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="137" s="8" customFormat="1" spans="1:7">
+    <row r="137" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A137" s="13" t="s">
         <v>377</v>
       </c>
@@ -9819,7 +9822,7 @@
       </c>
       <c r="G137" s="14"/>
     </row>
-    <row r="138" s="8" customFormat="1" spans="1:7">
+    <row r="138" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A138" s="13" t="s">
         <v>380</v>
       </c>
@@ -9840,7 +9843,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="139" s="8" customFormat="1" spans="1:7">
+    <row r="139" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A139" s="13" t="s">
         <v>383</v>
       </c>
@@ -9859,7 +9862,7 @@
       </c>
       <c r="G139" s="14"/>
     </row>
-    <row r="140" s="8" customFormat="1" spans="1:7">
+    <row r="140" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A140" s="13" t="s">
         <v>385</v>
       </c>
@@ -9878,7 +9881,7 @@
       </c>
       <c r="G140" s="14"/>
     </row>
-    <row r="141" s="8" customFormat="1" spans="1:7">
+    <row r="141" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A141" s="13" t="s">
         <v>387</v>
       </c>
@@ -9897,7 +9900,7 @@
       </c>
       <c r="G141" s="14"/>
     </row>
-    <row r="142" s="8" customFormat="1" spans="1:7">
+    <row r="142" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A142" s="13" t="s">
         <v>389</v>
       </c>
@@ -9916,7 +9919,7 @@
       </c>
       <c r="G142" s="14"/>
     </row>
-    <row r="143" s="8" customFormat="1" spans="1:7">
+    <row r="143" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A143" s="13" t="s">
         <v>391</v>
       </c>
@@ -9935,7 +9938,7 @@
       </c>
       <c r="G143" s="14"/>
     </row>
-    <row r="144" s="8" customFormat="1" spans="1:7">
+    <row r="144" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A144" s="13" t="s">
         <v>393</v>
       </c>
@@ -9954,7 +9957,7 @@
       </c>
       <c r="G144" s="14"/>
     </row>
-    <row r="145" s="8" customFormat="1" spans="1:7">
+    <row r="145" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A145" s="13" t="s">
         <v>395</v>
       </c>
@@ -9973,7 +9976,7 @@
       </c>
       <c r="G145" s="14"/>
     </row>
-    <row r="146" s="8" customFormat="1" spans="1:7">
+    <row r="146" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A146" s="13" t="s">
         <v>397</v>
       </c>
@@ -9994,7 +9997,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="147" s="8" customFormat="1" spans="1:7">
+    <row r="147" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A147" s="13" t="s">
         <v>399</v>
       </c>
@@ -10013,7 +10016,7 @@
       </c>
       <c r="G147" s="14"/>
     </row>
-    <row r="148" s="8" customFormat="1" spans="1:7">
+    <row r="148" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A148" s="13" t="s">
         <v>401</v>
       </c>
@@ -10034,7 +10037,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="149" s="8" customFormat="1" spans="1:7">
+    <row r="149" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A149" s="13" t="s">
         <v>404</v>
       </c>
@@ -10055,7 +10058,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="150" s="8" customFormat="1" spans="1:7">
+    <row r="150" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A150" s="13" t="s">
         <v>407</v>
       </c>
@@ -10074,7 +10077,7 @@
       </c>
       <c r="G150" s="14"/>
     </row>
-    <row r="151" s="8" customFormat="1" spans="1:7">
+    <row r="151" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A151" s="13" t="s">
         <v>409</v>
       </c>
@@ -10093,7 +10096,7 @@
       </c>
       <c r="G151" s="14"/>
     </row>
-    <row r="152" s="8" customFormat="1" spans="1:7">
+    <row r="152" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A152" s="13" t="s">
         <v>411</v>
       </c>
@@ -10112,7 +10115,7 @@
       </c>
       <c r="G152" s="14"/>
     </row>
-    <row r="153" s="8" customFormat="1" spans="1:7">
+    <row r="153" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A153" s="13" t="s">
         <v>413</v>
       </c>
@@ -10131,7 +10134,7 @@
       </c>
       <c r="G153" s="14"/>
     </row>
-    <row r="154" s="8" customFormat="1" spans="1:7">
+    <row r="154" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A154" s="13" t="s">
         <v>415</v>
       </c>
@@ -10150,7 +10153,7 @@
       </c>
       <c r="G154" s="14"/>
     </row>
-    <row r="155" s="8" customFormat="1" spans="1:7">
+    <row r="155" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A155" s="13" t="s">
         <v>417</v>
       </c>
@@ -10169,7 +10172,7 @@
       </c>
       <c r="G155" s="14"/>
     </row>
-    <row r="156" s="8" customFormat="1" spans="1:7">
+    <row r="156" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A156" s="13" t="s">
         <v>419</v>
       </c>
@@ -10190,7 +10193,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="157" s="8" customFormat="1" spans="1:7">
+    <row r="157" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A157" s="13" t="s">
         <v>422</v>
       </c>
@@ -10211,7 +10214,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="158" s="8" customFormat="1" spans="1:7">
+    <row r="158" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A158" s="13" t="s">
         <v>425</v>
       </c>
@@ -10230,7 +10233,7 @@
       </c>
       <c r="G158" s="14"/>
     </row>
-    <row r="159" s="8" customFormat="1" spans="1:7">
+    <row r="159" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A159" s="13" t="s">
         <v>427</v>
       </c>
@@ -10251,7 +10254,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="160" s="8" customFormat="1" spans="1:7">
+    <row r="160" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A160" s="13" t="s">
         <v>428</v>
       </c>
@@ -10270,7 +10273,7 @@
       </c>
       <c r="G160" s="14"/>
     </row>
-    <row r="161" s="8" customFormat="1" spans="1:7">
+    <row r="161" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A161" s="13" t="s">
         <v>430</v>
       </c>
@@ -10291,7 +10294,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="162" s="8" customFormat="1" spans="1:7">
+    <row r="162" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A162" s="13" t="s">
         <v>433</v>
       </c>
@@ -10310,7 +10313,7 @@
       </c>
       <c r="G162" s="14"/>
     </row>
-    <row r="163" s="8" customFormat="1" spans="1:7">
+    <row r="163" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A163" s="13" t="s">
         <v>435</v>
       </c>
@@ -10331,7 +10334,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="164" s="8" customFormat="1" spans="1:7">
+    <row r="164" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A164" s="13" t="s">
         <v>438</v>
       </c>
@@ -10350,7 +10353,7 @@
       </c>
       <c r="G164" s="14"/>
     </row>
-    <row r="165" s="8" customFormat="1" spans="1:7">
+    <row r="165" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A165" s="13" t="s">
         <v>439</v>
       </c>
@@ -10369,7 +10372,7 @@
       </c>
       <c r="G165" s="14"/>
     </row>
-    <row r="166" s="8" customFormat="1" spans="1:7">
+    <row r="166" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A166" s="13" t="s">
         <v>441</v>
       </c>
@@ -10390,7 +10393,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="167" s="8" customFormat="1" spans="1:7">
+    <row r="167" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A167" s="13" t="s">
         <v>444</v>
       </c>
@@ -10409,7 +10412,7 @@
       </c>
       <c r="G167" s="14"/>
     </row>
-    <row r="168" s="8" customFormat="1" spans="1:7">
+    <row r="168" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A168" s="13" t="s">
         <v>446</v>
       </c>
@@ -10430,7 +10433,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="169" s="8" customFormat="1" spans="1:7">
+    <row r="169" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A169" s="13" t="s">
         <v>448</v>
       </c>
@@ -10449,7 +10452,7 @@
       </c>
       <c r="G169" s="14"/>
     </row>
-    <row r="170" s="8" customFormat="1" spans="1:7">
+    <row r="170" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A170" s="13" t="s">
         <v>450</v>
       </c>
@@ -10468,7 +10471,7 @@
       </c>
       <c r="G170" s="14"/>
     </row>
-    <row r="171" s="8" customFormat="1" spans="1:7">
+    <row r="171" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A171" s="13" t="s">
         <v>452</v>
       </c>
@@ -10487,7 +10490,7 @@
       </c>
       <c r="G171" s="14"/>
     </row>
-    <row r="172" s="8" customFormat="1" spans="1:7">
+    <row r="172" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A172" s="13" t="s">
         <v>453</v>
       </c>
@@ -10506,7 +10509,7 @@
       </c>
       <c r="G172" s="14"/>
     </row>
-    <row r="173" s="8" customFormat="1" spans="1:7">
+    <row r="173" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A173" s="13" t="s">
         <v>455</v>
       </c>
@@ -10527,7 +10530,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="174" s="8" customFormat="1" spans="1:7">
+    <row r="174" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A174" s="13" t="s">
         <v>457</v>
       </c>
@@ -10546,7 +10549,7 @@
       </c>
       <c r="G174" s="14"/>
     </row>
-    <row r="175" s="8" customFormat="1" spans="1:7">
+    <row r="175" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A175" s="13" t="s">
         <v>458</v>
       </c>
@@ -10565,7 +10568,7 @@
       </c>
       <c r="G175" s="14"/>
     </row>
-    <row r="176" s="8" customFormat="1" spans="1:7">
+    <row r="176" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A176" s="13" t="s">
         <v>460</v>
       </c>
@@ -10584,7 +10587,7 @@
       </c>
       <c r="G176" s="14"/>
     </row>
-    <row r="177" s="8" customFormat="1" spans="1:7">
+    <row r="177" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A177" s="13" t="s">
         <v>462</v>
       </c>
@@ -10603,7 +10606,7 @@
       </c>
       <c r="G177" s="14"/>
     </row>
-    <row r="178" s="8" customFormat="1" spans="1:7">
+    <row r="178" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A178" s="13" t="s">
         <v>464</v>
       </c>
@@ -10622,7 +10625,7 @@
       </c>
       <c r="G178" s="14"/>
     </row>
-    <row r="179" s="8" customFormat="1" spans="1:7">
+    <row r="179" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A179" s="13" t="s">
         <v>466</v>
       </c>
@@ -10641,7 +10644,7 @@
       </c>
       <c r="G179" s="14"/>
     </row>
-    <row r="180" s="8" customFormat="1" spans="1:7">
+    <row r="180" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A180" s="13" t="s">
         <v>468</v>
       </c>
@@ -10660,7 +10663,7 @@
       </c>
       <c r="G180" s="14"/>
     </row>
-    <row r="181" s="8" customFormat="1" spans="1:7">
+    <row r="181" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A181" s="13" t="s">
         <v>470</v>
       </c>
@@ -10679,7 +10682,7 @@
       </c>
       <c r="G181" s="14"/>
     </row>
-    <row r="182" s="8" customFormat="1" spans="1:7">
+    <row r="182" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A182" s="13" t="s">
         <v>472</v>
       </c>
@@ -10698,7 +10701,7 @@
       </c>
       <c r="G182" s="14"/>
     </row>
-    <row r="183" s="8" customFormat="1" spans="1:7">
+    <row r="183" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A183" s="13" t="s">
         <v>474</v>
       </c>
@@ -10717,7 +10720,7 @@
       </c>
       <c r="G183" s="14"/>
     </row>
-    <row r="184" s="8" customFormat="1" spans="1:7">
+    <row r="184" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A184" s="13" t="s">
         <v>476</v>
       </c>
@@ -10736,7 +10739,7 @@
       </c>
       <c r="G184" s="14"/>
     </row>
-    <row r="185" s="8" customFormat="1" spans="1:7">
+    <row r="185" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A185" s="13" t="s">
         <v>478</v>
       </c>
@@ -10757,7 +10760,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="186" s="8" customFormat="1" spans="1:7">
+    <row r="186" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A186" s="13" t="s">
         <v>478</v>
       </c>
@@ -10778,7 +10781,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="187" s="8" customFormat="1" spans="1:7">
+    <row r="187" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A187" s="13" t="s">
         <v>481</v>
       </c>
@@ -10799,7 +10802,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="188" s="8" customFormat="1" spans="1:7">
+    <row r="188" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A188" s="13" t="s">
         <v>481</v>
       </c>
@@ -10820,7 +10823,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="189" s="8" customFormat="1" spans="1:7">
+    <row r="189" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A189" s="13" t="s">
         <v>484</v>
       </c>
@@ -10841,7 +10844,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="190" s="8" customFormat="1" spans="1:7">
+    <row r="190" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A190" s="13" t="s">
         <v>484</v>
       </c>
@@ -10862,7 +10865,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="191" s="8" customFormat="1" spans="1:7">
+    <row r="191" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A191" s="13" t="s">
         <v>485</v>
       </c>
@@ -10883,7 +10886,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="192" s="8" customFormat="1" spans="1:7">
+    <row r="192" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A192" s="13" t="s">
         <v>485</v>
       </c>
@@ -10904,7 +10907,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="193" s="8" customFormat="1" spans="1:7">
+    <row r="193" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A193" s="13" t="s">
         <v>488</v>
       </c>
@@ -10925,7 +10928,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="194" s="8" customFormat="1" spans="1:7">
+    <row r="194" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A194" s="13" t="s">
         <v>488</v>
       </c>
@@ -10946,7 +10949,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="195" s="8" customFormat="1" spans="1:7">
+    <row r="195" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A195" s="13" t="s">
         <v>490</v>
       </c>
@@ -10967,7 +10970,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="196" s="8" customFormat="1" spans="1:7">
+    <row r="196" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A196" s="13" t="s">
         <v>490</v>
       </c>
@@ -10988,7 +10991,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="197" s="8" customFormat="1" spans="1:7">
+    <row r="197" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A197" s="13" t="s">
         <v>492</v>
       </c>
@@ -11009,7 +11012,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="198" s="8" customFormat="1" spans="1:7">
+    <row r="198" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A198" s="13" t="s">
         <v>495</v>
       </c>
@@ -11030,7 +11033,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="199" s="8" customFormat="1" spans="1:7">
+    <row r="199" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A199" s="13" t="s">
         <v>496</v>
       </c>
@@ -11049,7 +11052,7 @@
       </c>
       <c r="G199" s="14"/>
     </row>
-    <row r="200" s="8" customFormat="1" spans="1:7">
+    <row r="200" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A200" s="13" t="s">
         <v>497</v>
       </c>
@@ -11068,7 +11071,7 @@
       </c>
       <c r="G200" s="14"/>
     </row>
-    <row r="201" s="8" customFormat="1" spans="1:7">
+    <row r="201" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A201" s="13" t="s">
         <v>498</v>
       </c>
@@ -11087,7 +11090,7 @@
       </c>
       <c r="G201" s="14"/>
     </row>
-    <row r="202" s="8" customFormat="1" spans="1:7">
+    <row r="202" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A202" s="13" t="s">
         <v>500</v>
       </c>
@@ -11106,7 +11109,7 @@
       </c>
       <c r="G202" s="14"/>
     </row>
-    <row r="203" s="8" customFormat="1" spans="1:7">
+    <row r="203" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A203" s="13" t="s">
         <v>501</v>
       </c>
@@ -11125,7 +11128,7 @@
       </c>
       <c r="G203" s="14"/>
     </row>
-    <row r="204" s="8" customFormat="1" spans="1:7">
+    <row r="204" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A204" s="13" t="s">
         <v>502</v>
       </c>
@@ -11146,7 +11149,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="205" s="8" customFormat="1" spans="1:7">
+    <row r="205" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A205" s="13" t="s">
         <v>504</v>
       </c>
@@ -11165,7 +11168,7 @@
       </c>
       <c r="G205" s="14"/>
     </row>
-    <row r="206" s="8" customFormat="1" spans="1:7">
+    <row r="206" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A206" s="13" t="s">
         <v>505</v>
       </c>
@@ -11184,7 +11187,7 @@
       </c>
       <c r="G206" s="14"/>
     </row>
-    <row r="207" s="8" customFormat="1" spans="1:7">
+    <row r="207" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A207" s="13" t="s">
         <v>506</v>
       </c>
@@ -11203,7 +11206,7 @@
       </c>
       <c r="G207" s="14"/>
     </row>
-    <row r="208" s="8" customFormat="1" spans="1:7">
+    <row r="208" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A208" s="13" t="s">
         <v>507</v>
       </c>
@@ -11222,7 +11225,7 @@
       </c>
       <c r="G208" s="14"/>
     </row>
-    <row r="209" s="8" customFormat="1" spans="1:7">
+    <row r="209" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A209" s="13" t="s">
         <v>508</v>
       </c>
@@ -11243,7 +11246,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="210" s="8" customFormat="1" spans="1:7">
+    <row r="210" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A210" s="13" t="s">
         <v>509</v>
       </c>
@@ -11264,7 +11267,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="211" s="8" customFormat="1" spans="1:7">
+    <row r="211" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A211" s="13" t="s">
         <v>510</v>
       </c>
@@ -11285,7 +11288,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="212" s="8" customFormat="1" spans="1:7">
+    <row r="212" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A212" s="13" t="s">
         <v>512</v>
       </c>
@@ -11306,7 +11309,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="213" s="8" customFormat="1" spans="1:7">
+    <row r="213" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A213" s="13" t="s">
         <v>514</v>
       </c>
@@ -11325,7 +11328,7 @@
       </c>
       <c r="G213" s="14"/>
     </row>
-    <row r="214" s="8" customFormat="1" spans="1:7">
+    <row r="214" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A214" s="13" t="s">
         <v>515</v>
       </c>
@@ -11344,7 +11347,7 @@
       </c>
       <c r="G214" s="14"/>
     </row>
-    <row r="215" s="8" customFormat="1" spans="1:7">
+    <row r="215" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A215" s="13" t="s">
         <v>516</v>
       </c>
@@ -11363,7 +11366,7 @@
       </c>
       <c r="G215" s="14"/>
     </row>
-    <row r="216" s="8" customFormat="1" spans="1:7">
+    <row r="216" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A216" s="13" t="s">
         <v>517</v>
       </c>
@@ -11382,7 +11385,7 @@
       </c>
       <c r="G216" s="14"/>
     </row>
-    <row r="217" s="8" customFormat="1" spans="1:7">
+    <row r="217" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A217" s="13" t="s">
         <v>518</v>
       </c>
@@ -11401,7 +11404,7 @@
       </c>
       <c r="G217" s="14"/>
     </row>
-    <row r="218" s="8" customFormat="1" spans="1:7">
+    <row r="218" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A218" s="13" t="s">
         <v>519</v>
       </c>
@@ -11422,7 +11425,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="219" s="8" customFormat="1" spans="1:7">
+    <row r="219" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A219" s="13" t="s">
         <v>520</v>
       </c>
@@ -11443,7 +11446,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="220" s="8" customFormat="1" spans="1:7">
+    <row r="220" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A220" s="13" t="s">
         <v>521</v>
       </c>
@@ -11464,7 +11467,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="221" s="8" customFormat="1" spans="1:7">
+    <row r="221" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A221" s="13" t="s">
         <v>522</v>
       </c>
@@ -11485,7 +11488,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="222" s="8" customFormat="1" spans="1:7">
+    <row r="222" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A222" s="13" t="s">
         <v>525</v>
       </c>
@@ -11506,7 +11509,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="223" s="8" customFormat="1" spans="1:7">
+    <row r="223" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A223" s="13" t="s">
         <v>527</v>
       </c>
@@ -11527,7 +11530,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="224" s="8" customFormat="1" spans="1:7">
+    <row r="224" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A224" s="13" t="s">
         <v>528</v>
       </c>
@@ -11546,7 +11549,7 @@
       </c>
       <c r="G224" s="14"/>
     </row>
-    <row r="225" s="8" customFormat="1" spans="1:7">
+    <row r="225" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A225" s="13" t="s">
         <v>529</v>
       </c>
@@ -11565,7 +11568,7 @@
       </c>
       <c r="G225" s="14"/>
     </row>
-    <row r="226" s="8" customFormat="1" spans="1:7">
+    <row r="226" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A226" s="13" t="s">
         <v>530</v>
       </c>
@@ -11584,7 +11587,7 @@
       </c>
       <c r="G226" s="14"/>
     </row>
-    <row r="227" s="8" customFormat="1" spans="1:7">
+    <row r="227" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A227" s="13" t="s">
         <v>531</v>
       </c>
@@ -11603,7 +11606,7 @@
       </c>
       <c r="G227" s="14"/>
     </row>
-    <row r="228" s="8" customFormat="1" spans="1:7">
+    <row r="228" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A228" s="13" t="s">
         <v>532</v>
       </c>
@@ -11622,7 +11625,7 @@
       </c>
       <c r="G228" s="14"/>
     </row>
-    <row r="229" s="8" customFormat="1" spans="1:7">
+    <row r="229" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A229" s="13" t="s">
         <v>533</v>
       </c>
@@ -11641,7 +11644,7 @@
       </c>
       <c r="G229" s="14"/>
     </row>
-    <row r="230" s="8" customFormat="1" spans="1:7">
+    <row r="230" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A230" s="13" t="s">
         <v>534</v>
       </c>
@@ -11662,7 +11665,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="231" s="8" customFormat="1" spans="1:7">
+    <row r="231" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A231" s="13" t="s">
         <v>536</v>
       </c>
@@ -11683,7 +11686,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="232" s="8" customFormat="1" spans="1:7">
+    <row r="232" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A232" s="13" t="s">
         <v>538</v>
       </c>
@@ -11704,7 +11707,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="233" s="8" customFormat="1" spans="1:7">
+    <row r="233" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A233" s="13" t="s">
         <v>540</v>
       </c>
@@ -11725,7 +11728,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="234" s="8" customFormat="1" spans="1:7">
+    <row r="234" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A234" s="13" t="s">
         <v>542</v>
       </c>
@@ -11744,7 +11747,7 @@
       </c>
       <c r="G234" s="14"/>
     </row>
-    <row r="235" s="8" customFormat="1" spans="1:7">
+    <row r="235" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A235" s="13" t="s">
         <v>544</v>
       </c>
@@ -11763,7 +11766,7 @@
       </c>
       <c r="G235" s="14"/>
     </row>
-    <row r="236" s="8" customFormat="1" spans="1:7">
+    <row r="236" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A236" s="13" t="s">
         <v>546</v>
       </c>
@@ -11782,7 +11785,7 @@
       </c>
       <c r="G236" s="14"/>
     </row>
-    <row r="237" s="8" customFormat="1" spans="1:7">
+    <row r="237" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A237" s="13" t="s">
         <v>548</v>
       </c>
@@ -11803,7 +11806,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="238" s="8" customFormat="1" spans="1:7">
+    <row r="238" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A238" s="13" t="s">
         <v>551</v>
       </c>
@@ -11822,7 +11825,7 @@
       </c>
       <c r="G238" s="14"/>
     </row>
-    <row r="239" s="8" customFormat="1" spans="1:7">
+    <row r="239" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A239" s="13" t="s">
         <v>553</v>
       </c>
@@ -11841,7 +11844,7 @@
       </c>
       <c r="G239" s="14"/>
     </row>
-    <row r="240" s="8" customFormat="1" spans="1:7">
+    <row r="240" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A240" s="13" t="s">
         <v>554</v>
       </c>
@@ -11860,7 +11863,7 @@
       </c>
       <c r="G240" s="14"/>
     </row>
-    <row r="241" s="8" customFormat="1" spans="1:7">
+    <row r="241" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A241" s="13" t="s">
         <v>556</v>
       </c>
@@ -11881,7 +11884,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="242" s="8" customFormat="1" spans="1:7">
+    <row r="242" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A242" s="13" t="s">
         <v>559</v>
       </c>
@@ -11900,7 +11903,7 @@
       </c>
       <c r="G242" s="14"/>
     </row>
-    <row r="243" s="8" customFormat="1" spans="1:7">
+    <row r="243" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A243" s="13" t="s">
         <v>561</v>
       </c>
@@ -11919,7 +11922,7 @@
       </c>
       <c r="G243" s="14"/>
     </row>
-    <row r="244" s="8" customFormat="1" spans="1:7">
+    <row r="244" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A244" s="13" t="s">
         <v>563</v>
       </c>
@@ -11938,7 +11941,7 @@
       </c>
       <c r="G244" s="14"/>
     </row>
-    <row r="245" s="8" customFormat="1" spans="1:7">
+    <row r="245" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A245" s="13" t="s">
         <v>565</v>
       </c>
@@ -11959,7 +11962,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="246" s="8" customFormat="1" spans="1:7">
+    <row r="246" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A246" s="13" t="s">
         <v>567</v>
       </c>
@@ -11978,7 +11981,7 @@
       </c>
       <c r="G246" s="14"/>
     </row>
-    <row r="247" s="8" customFormat="1" spans="1:7">
+    <row r="247" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A247" s="13" t="s">
         <v>569</v>
       </c>
@@ -11997,7 +12000,7 @@
       </c>
       <c r="G247" s="14"/>
     </row>
-    <row r="248" s="8" customFormat="1" spans="1:7">
+    <row r="248" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A248" s="13" t="s">
         <v>570</v>
       </c>
@@ -12018,7 +12021,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="249" s="8" customFormat="1" spans="1:7">
+    <row r="249" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A249" s="13" t="s">
         <v>572</v>
       </c>
@@ -12037,7 +12040,7 @@
       </c>
       <c r="G249" s="14"/>
     </row>
-    <row r="250" s="8" customFormat="1" spans="1:7">
+    <row r="250" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A250" s="13" t="s">
         <v>574</v>
       </c>
@@ -12056,7 +12059,7 @@
       </c>
       <c r="G250" s="14"/>
     </row>
-    <row r="251" s="8" customFormat="1" spans="1:7">
+    <row r="251" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A251" s="13" t="s">
         <v>576</v>
       </c>
@@ -12075,7 +12078,7 @@
       </c>
       <c r="G251" s="14"/>
     </row>
-    <row r="252" s="8" customFormat="1" spans="1:7">
+    <row r="252" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A252" s="13" t="s">
         <v>578</v>
       </c>
@@ -12096,7 +12099,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="253" s="8" customFormat="1" spans="1:7">
+    <row r="253" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A253" s="13" t="s">
         <v>580</v>
       </c>
@@ -12115,7 +12118,7 @@
       </c>
       <c r="G253" s="14"/>
     </row>
-    <row r="254" s="8" customFormat="1" spans="1:7">
+    <row r="254" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A254" s="13" t="s">
         <v>582</v>
       </c>
@@ -12134,7 +12137,7 @@
       </c>
       <c r="G254" s="14"/>
     </row>
-    <row r="255" s="8" customFormat="1" spans="1:7">
+    <row r="255" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A255" s="13" t="s">
         <v>583</v>
       </c>
@@ -12153,7 +12156,7 @@
       </c>
       <c r="G255" s="14"/>
     </row>
-    <row r="256" s="8" customFormat="1" spans="1:7">
+    <row r="256" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A256" s="13" t="s">
         <v>584</v>
       </c>
@@ -12172,7 +12175,7 @@
       </c>
       <c r="G256" s="14"/>
     </row>
-    <row r="257" s="8" customFormat="1" spans="1:7">
+    <row r="257" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A257" s="13" t="s">
         <v>585</v>
       </c>
@@ -12191,7 +12194,7 @@
       </c>
       <c r="G257" s="14"/>
     </row>
-    <row r="258" s="8" customFormat="1" spans="1:7">
+    <row r="258" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A258" s="13" t="s">
         <v>587</v>
       </c>
@@ -12210,7 +12213,7 @@
       </c>
       <c r="G258" s="14"/>
     </row>
-    <row r="259" s="8" customFormat="1" spans="1:7">
+    <row r="259" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A259" s="13" t="s">
         <v>588</v>
       </c>
@@ -12229,7 +12232,7 @@
       </c>
       <c r="G259" s="14"/>
     </row>
-    <row r="260" s="8" customFormat="1" spans="1:7">
+    <row r="260" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A260" s="13" t="s">
         <v>589</v>
       </c>
@@ -12248,7 +12251,7 @@
       </c>
       <c r="G260" s="14"/>
     </row>
-    <row r="261" s="8" customFormat="1" spans="1:7">
+    <row r="261" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A261" s="13" t="s">
         <v>590</v>
       </c>
@@ -12267,7 +12270,7 @@
       </c>
       <c r="G261" s="14"/>
     </row>
-    <row r="262" s="8" customFormat="1" spans="1:7">
+    <row r="262" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A262" s="13" t="s">
         <v>591</v>
       </c>
@@ -12288,7 +12291,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="263" s="8" customFormat="1" spans="1:7">
+    <row r="263" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A263" s="13" t="s">
         <v>592</v>
       </c>
@@ -12307,7 +12310,7 @@
       </c>
       <c r="G263" s="14"/>
     </row>
-    <row r="264" s="8" customFormat="1" spans="1:7">
+    <row r="264" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A264" s="13" t="s">
         <v>593</v>
       </c>
@@ -12326,7 +12329,7 @@
       </c>
       <c r="G264" s="14"/>
     </row>
-    <row r="265" s="8" customFormat="1" spans="1:7">
+    <row r="265" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A265" s="13" t="s">
         <v>594</v>
       </c>
@@ -12345,7 +12348,7 @@
       </c>
       <c r="G265" s="14"/>
     </row>
-    <row r="266" s="8" customFormat="1" spans="1:7">
+    <row r="266" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A266" s="13" t="s">
         <v>596</v>
       </c>
@@ -12364,7 +12367,7 @@
       </c>
       <c r="G266" s="14"/>
     </row>
-    <row r="267" s="8" customFormat="1" spans="1:7">
+    <row r="267" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A267" s="13" t="s">
         <v>597</v>
       </c>
@@ -12383,7 +12386,7 @@
       </c>
       <c r="G267" s="14"/>
     </row>
-    <row r="268" s="8" customFormat="1" spans="1:7">
+    <row r="268" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A268" s="13" t="s">
         <v>598</v>
       </c>
@@ -12402,7 +12405,7 @@
       </c>
       <c r="G268" s="14"/>
     </row>
-    <row r="269" s="8" customFormat="1" spans="1:7">
+    <row r="269" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A269" s="13" t="s">
         <v>599</v>
       </c>
@@ -12421,7 +12424,7 @@
       </c>
       <c r="G269" s="14"/>
     </row>
-    <row r="270" s="8" customFormat="1" spans="1:7">
+    <row r="270" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A270" s="13" t="s">
         <v>601</v>
       </c>
@@ -12440,7 +12443,7 @@
       </c>
       <c r="G270" s="14"/>
     </row>
-    <row r="271" s="8" customFormat="1" spans="1:7">
+    <row r="271" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A271" s="13" t="s">
         <v>603</v>
       </c>
@@ -12459,7 +12462,7 @@
       </c>
       <c r="G271" s="14"/>
     </row>
-    <row r="272" s="8" customFormat="1" spans="1:7">
+    <row r="272" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A272" s="13" t="s">
         <v>604</v>
       </c>
@@ -12478,7 +12481,7 @@
       </c>
       <c r="G272" s="14"/>
     </row>
-    <row r="273" s="8" customFormat="1" spans="1:7">
+    <row r="273" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A273" s="13" t="s">
         <v>605</v>
       </c>
@@ -12497,7 +12500,7 @@
       </c>
       <c r="G273" s="14"/>
     </row>
-    <row r="274" s="8" customFormat="1" spans="1:7">
+    <row r="274" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A274" s="13" t="s">
         <v>606</v>
       </c>
@@ -12516,7 +12519,7 @@
       </c>
       <c r="G274" s="14"/>
     </row>
-    <row r="275" s="8" customFormat="1" spans="1:7">
+    <row r="275" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A275" s="13" t="s">
         <v>608</v>
       </c>
@@ -12535,7 +12538,7 @@
       </c>
       <c r="G275" s="14"/>
     </row>
-    <row r="276" s="8" customFormat="1" spans="1:7">
+    <row r="276" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A276" s="13" t="s">
         <v>609</v>
       </c>
@@ -12554,7 +12557,7 @@
       </c>
       <c r="G276" s="14"/>
     </row>
-    <row r="277" s="8" customFormat="1" spans="1:7">
+    <row r="277" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A277" s="13" t="s">
         <v>610</v>
       </c>
@@ -12573,7 +12576,7 @@
       </c>
       <c r="G277" s="14"/>
     </row>
-    <row r="278" s="8" customFormat="1" spans="1:7">
+    <row r="278" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A278" s="13" t="s">
         <v>611</v>
       </c>
@@ -12592,7 +12595,7 @@
       </c>
       <c r="G278" s="14"/>
     </row>
-    <row r="279" s="8" customFormat="1" spans="1:7">
+    <row r="279" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A279" s="13" t="s">
         <v>612</v>
       </c>
@@ -12611,7 +12614,7 @@
       </c>
       <c r="G279" s="14"/>
     </row>
-    <row r="280" s="8" customFormat="1" spans="1:7">
+    <row r="280" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A280" s="13" t="s">
         <v>613</v>
       </c>
@@ -12630,7 +12633,7 @@
       </c>
       <c r="G280" s="14"/>
     </row>
-    <row r="281" s="8" customFormat="1" spans="1:7">
+    <row r="281" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A281" s="13" t="s">
         <v>614</v>
       </c>
@@ -12649,7 +12652,7 @@
       </c>
       <c r="G281" s="14"/>
     </row>
-    <row r="282" s="8" customFormat="1" spans="1:7">
+    <row r="282" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A282" s="13" t="s">
         <v>615</v>
       </c>
@@ -12668,7 +12671,7 @@
       </c>
       <c r="G282" s="14"/>
     </row>
-    <row r="283" s="8" customFormat="1" spans="1:7">
+    <row r="283" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A283" s="13" t="s">
         <v>616</v>
       </c>
@@ -12689,7 +12692,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="284" s="8" customFormat="1" spans="1:7">
+    <row r="284" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A284" s="13" t="s">
         <v>619</v>
       </c>
@@ -12708,7 +12711,7 @@
       </c>
       <c r="G284" s="14"/>
     </row>
-    <row r="285" s="8" customFormat="1" spans="1:7">
+    <row r="285" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A285" s="13" t="s">
         <v>620</v>
       </c>
@@ -12727,7 +12730,7 @@
       </c>
       <c r="G285" s="14"/>
     </row>
-    <row r="286" s="8" customFormat="1" spans="1:7">
+    <row r="286" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A286" s="13" t="s">
         <v>621</v>
       </c>
@@ -12746,7 +12749,7 @@
       </c>
       <c r="G286" s="14"/>
     </row>
-    <row r="287" s="8" customFormat="1" spans="1:7">
+    <row r="287" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A287" s="13" t="s">
         <v>622</v>
       </c>
@@ -12765,7 +12768,7 @@
       </c>
       <c r="G287" s="14"/>
     </row>
-    <row r="288" s="8" customFormat="1" spans="1:7">
+    <row r="288" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A288" s="13" t="s">
         <v>623</v>
       </c>
@@ -12784,7 +12787,7 @@
       </c>
       <c r="G288" s="14"/>
     </row>
-    <row r="289" s="8" customFormat="1" spans="1:7">
+    <row r="289" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A289" s="13" t="s">
         <v>624</v>
       </c>
@@ -12803,7 +12806,7 @@
       </c>
       <c r="G289" s="14"/>
     </row>
-    <row r="290" s="8" customFormat="1" spans="1:7">
+    <row r="290" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A290" s="13" t="s">
         <v>626</v>
       </c>
@@ -12822,7 +12825,7 @@
       </c>
       <c r="G290" s="14"/>
     </row>
-    <row r="291" s="8" customFormat="1" spans="1:7">
+    <row r="291" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A291" s="13" t="s">
         <v>628</v>
       </c>
@@ -12841,7 +12844,7 @@
       </c>
       <c r="G291" s="14"/>
     </row>
-    <row r="292" s="8" customFormat="1" spans="1:7">
+    <row r="292" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A292" s="13" t="s">
         <v>629</v>
       </c>
@@ -12860,7 +12863,7 @@
       </c>
       <c r="G292" s="14"/>
     </row>
-    <row r="293" s="8" customFormat="1" spans="1:7">
+    <row r="293" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A293" s="13" t="s">
         <v>630</v>
       </c>
@@ -12879,7 +12882,7 @@
       </c>
       <c r="G293" s="14"/>
     </row>
-    <row r="294" s="8" customFormat="1" spans="1:7">
+    <row r="294" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A294" s="13" t="s">
         <v>631</v>
       </c>
@@ -12898,7 +12901,7 @@
       </c>
       <c r="G294" s="14"/>
     </row>
-    <row r="295" s="8" customFormat="1" spans="1:7">
+    <row r="295" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A295" s="13" t="s">
         <v>632</v>
       </c>
@@ -12917,7 +12920,7 @@
       </c>
       <c r="G295" s="14"/>
     </row>
-    <row r="296" s="8" customFormat="1" spans="1:7">
+    <row r="296" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A296" s="13" t="s">
         <v>634</v>
       </c>
@@ -12936,7 +12939,7 @@
       </c>
       <c r="G296" s="14"/>
     </row>
-    <row r="297" s="8" customFormat="1" spans="1:7">
+    <row r="297" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A297" s="13" t="s">
         <v>635</v>
       </c>
@@ -12955,7 +12958,7 @@
       </c>
       <c r="G297" s="14"/>
     </row>
-    <row r="298" s="8" customFormat="1" spans="1:7">
+    <row r="298" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A298" s="13" t="s">
         <v>637</v>
       </c>
@@ -12974,7 +12977,7 @@
       </c>
       <c r="G298" s="14"/>
     </row>
-    <row r="299" s="8" customFormat="1" spans="1:7">
+    <row r="299" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A299" s="13" t="s">
         <v>639</v>
       </c>
@@ -12993,7 +12996,7 @@
       </c>
       <c r="G299" s="14"/>
     </row>
-    <row r="300" s="8" customFormat="1" spans="1:7">
+    <row r="300" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A300" s="13" t="s">
         <v>640</v>
       </c>
@@ -13012,7 +13015,7 @@
       </c>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" s="8" customFormat="1" spans="1:7">
+    <row r="301" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A301" s="13" t="s">
         <v>641</v>
       </c>
@@ -13031,7 +13034,7 @@
       </c>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" s="8" customFormat="1" spans="1:7">
+    <row r="302" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A302" s="13" t="s">
         <v>642</v>
       </c>
@@ -13050,7 +13053,7 @@
       </c>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" s="8" customFormat="1" spans="1:7">
+    <row r="303" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A303" s="13" t="s">
         <v>643</v>
       </c>
@@ -13069,7 +13072,7 @@
       </c>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" s="8" customFormat="1" spans="1:7">
+    <row r="304" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A304" s="13" t="s">
         <v>644</v>
       </c>
@@ -13088,7 +13091,7 @@
       </c>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" s="8" customFormat="1" spans="1:7">
+    <row r="305" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A305" s="13" t="s">
         <v>645</v>
       </c>
@@ -13107,7 +13110,7 @@
       </c>
       <c r="G305" s="14"/>
     </row>
-    <row r="306" s="8" customFormat="1" spans="1:7">
+    <row r="306" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A306" s="13" t="s">
         <v>647</v>
       </c>
@@ -13128,7 +13131,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="307" s="8" customFormat="1" spans="1:7">
+    <row r="307" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A307" s="13" t="s">
         <v>649</v>
       </c>
@@ -13147,7 +13150,7 @@
       </c>
       <c r="G307" s="14"/>
     </row>
-    <row r="308" s="8" customFormat="1" spans="1:7">
+    <row r="308" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A308" s="13" t="s">
         <v>650</v>
       </c>
@@ -13166,7 +13169,7 @@
       </c>
       <c r="G308" s="14"/>
     </row>
-    <row r="309" s="8" customFormat="1" spans="1:7">
+    <row r="309" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A309" s="13" t="s">
         <v>652</v>
       </c>
@@ -13185,7 +13188,7 @@
       </c>
       <c r="G309" s="14"/>
     </row>
-    <row r="310" s="8" customFormat="1" spans="1:7">
+    <row r="310" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A310" s="13" t="s">
         <v>653</v>
       </c>
@@ -13206,7 +13209,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="311" s="8" customFormat="1" spans="1:7">
+    <row r="311" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A311" s="13" t="s">
         <v>655</v>
       </c>
@@ -13225,7 +13228,7 @@
       </c>
       <c r="G311" s="14"/>
     </row>
-    <row r="312" s="8" customFormat="1" spans="1:7">
+    <row r="312" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A312" s="13" t="s">
         <v>656</v>
       </c>
@@ -13244,7 +13247,7 @@
       </c>
       <c r="G312" s="14"/>
     </row>
-    <row r="313" s="8" customFormat="1" spans="1:7">
+    <row r="313" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A313" s="13" t="s">
         <v>657</v>
       </c>
@@ -13263,7 +13266,7 @@
       </c>
       <c r="G313" s="14"/>
     </row>
-    <row r="314" s="8" customFormat="1" spans="1:7">
+    <row r="314" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A314" s="13" t="s">
         <v>658</v>
       </c>
@@ -13282,7 +13285,7 @@
       </c>
       <c r="G314" s="14"/>
     </row>
-    <row r="315" s="8" customFormat="1" spans="1:7">
+    <row r="315" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A315" s="13" t="s">
         <v>660</v>
       </c>
@@ -13301,7 +13304,7 @@
       </c>
       <c r="G315" s="14"/>
     </row>
-    <row r="316" s="8" customFormat="1" spans="1:7">
+    <row r="316" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A316" s="13" t="s">
         <v>662</v>
       </c>
@@ -13320,7 +13323,7 @@
       </c>
       <c r="G316" s="14"/>
     </row>
-    <row r="317" s="8" customFormat="1" spans="1:7">
+    <row r="317" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A317" s="13" t="s">
         <v>664</v>
       </c>
@@ -13339,7 +13342,7 @@
       </c>
       <c r="G317" s="14"/>
     </row>
-    <row r="318" s="8" customFormat="1" spans="1:7">
+    <row r="318" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A318" s="13" t="s">
         <v>666</v>
       </c>
@@ -13358,7 +13361,7 @@
       </c>
       <c r="G318" s="14"/>
     </row>
-    <row r="319" s="8" customFormat="1" spans="1:7">
+    <row r="319" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A319" s="13" t="s">
         <v>668</v>
       </c>
@@ -13377,7 +13380,7 @@
       </c>
       <c r="G319" s="14"/>
     </row>
-    <row r="320" s="8" customFormat="1" spans="1:7">
+    <row r="320" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A320" s="13" t="s">
         <v>670</v>
       </c>
@@ -13396,7 +13399,7 @@
       </c>
       <c r="G320" s="14"/>
     </row>
-    <row r="321" s="8" customFormat="1" spans="1:7">
+    <row r="321" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A321" s="13" t="s">
         <v>672</v>
       </c>
@@ -13415,7 +13418,7 @@
       </c>
       <c r="G321" s="14"/>
     </row>
-    <row r="322" s="8" customFormat="1" spans="1:7">
+    <row r="322" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A322" s="13" t="s">
         <v>673</v>
       </c>
@@ -13434,7 +13437,7 @@
       </c>
       <c r="G322" s="14"/>
     </row>
-    <row r="323" s="8" customFormat="1" spans="1:7">
+    <row r="323" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A323" s="13" t="s">
         <v>674</v>
       </c>
@@ -13453,7 +13456,7 @@
       </c>
       <c r="G323" s="14"/>
     </row>
-    <row r="324" s="8" customFormat="1" spans="1:7">
+    <row r="324" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A324" s="13" t="s">
         <v>676</v>
       </c>
@@ -13472,7 +13475,7 @@
       </c>
       <c r="G324" s="14"/>
     </row>
-    <row r="325" s="8" customFormat="1" spans="1:7">
+    <row r="325" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A325" s="13" t="s">
         <v>677</v>
       </c>
@@ -13491,7 +13494,7 @@
       </c>
       <c r="G325" s="14"/>
     </row>
-    <row r="326" s="9" customFormat="1" spans="1:7">
+    <row r="326" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A326" s="13" t="s">
         <v>678</v>
       </c>
@@ -13510,7 +13513,7 @@
       </c>
       <c r="G326" s="14"/>
     </row>
-    <row r="327" s="9" customFormat="1" spans="1:7">
+    <row r="327" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A327" s="13" t="s">
         <v>680</v>
       </c>
@@ -13529,7 +13532,7 @@
       </c>
       <c r="G327" s="14"/>
     </row>
-    <row r="328" s="9" customFormat="1" spans="1:7">
+    <row r="328" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A328" s="13" t="s">
         <v>681</v>
       </c>
@@ -13548,7 +13551,7 @@
       </c>
       <c r="G328" s="14"/>
     </row>
-    <row r="329" s="9" customFormat="1" spans="1:7">
+    <row r="329" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A329" s="13" t="s">
         <v>683</v>
       </c>
@@ -13567,7 +13570,7 @@
       </c>
       <c r="G329" s="14"/>
     </row>
-    <row r="330" s="9" customFormat="1" spans="1:7">
+    <row r="330" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A330" s="13" t="s">
         <v>684</v>
       </c>
@@ -13586,7 +13589,7 @@
       </c>
       <c r="G330" s="14"/>
     </row>
-    <row r="331" s="9" customFormat="1" spans="1:7">
+    <row r="331" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A331" s="13" t="s">
         <v>685</v>
       </c>
@@ -13605,7 +13608,7 @@
       </c>
       <c r="G331" s="14"/>
     </row>
-    <row r="332" s="9" customFormat="1" spans="1:7">
+    <row r="332" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A332" s="13" t="s">
         <v>686</v>
       </c>
@@ -13624,7 +13627,7 @@
       </c>
       <c r="G332" s="14"/>
     </row>
-    <row r="333" s="9" customFormat="1" spans="1:7">
+    <row r="333" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A333" s="13" t="s">
         <v>688</v>
       </c>
@@ -13643,7 +13646,7 @@
       </c>
       <c r="G333" s="14"/>
     </row>
-    <row r="334" s="9" customFormat="1" spans="1:7">
+    <row r="334" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A334" s="13" t="s">
         <v>690</v>
       </c>
@@ -13664,7 +13667,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="335" s="9" customFormat="1" spans="1:7">
+    <row r="335" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A335" s="13" t="s">
         <v>692</v>
       </c>
@@ -13683,7 +13686,7 @@
       </c>
       <c r="G335" s="14"/>
     </row>
-    <row r="336" s="9" customFormat="1" spans="1:7">
+    <row r="336" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A336" s="13" t="s">
         <v>693</v>
       </c>
@@ -13702,7 +13705,7 @@
       </c>
       <c r="G336" s="14"/>
     </row>
-    <row r="337" s="9" customFormat="1" spans="1:7">
+    <row r="337" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A337" s="13" t="s">
         <v>694</v>
       </c>
@@ -13721,7 +13724,7 @@
       </c>
       <c r="G337" s="14"/>
     </row>
-    <row r="338" s="9" customFormat="1" spans="1:7">
+    <row r="338" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A338" s="13" t="s">
         <v>695</v>
       </c>
@@ -13740,7 +13743,7 @@
       </c>
       <c r="G338" s="14"/>
     </row>
-    <row r="339" s="9" customFormat="1" spans="1:7">
+    <row r="339" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A339" s="13" t="s">
         <v>696</v>
       </c>
@@ -13759,7 +13762,7 @@
       </c>
       <c r="G339" s="14"/>
     </row>
-    <row r="340" s="9" customFormat="1" spans="1:7">
+    <row r="340" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A340" s="13" t="s">
         <v>697</v>
       </c>
@@ -13778,7 +13781,7 @@
       </c>
       <c r="G340" s="14"/>
     </row>
-    <row r="341" s="9" customFormat="1" spans="1:7">
+    <row r="341" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A341" s="13" t="s">
         <v>698</v>
       </c>
@@ -13797,7 +13800,7 @@
       </c>
       <c r="G341" s="14"/>
     </row>
-    <row r="342" s="9" customFormat="1" spans="1:7">
+    <row r="342" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A342" s="13" t="s">
         <v>699</v>
       </c>
@@ -13818,7 +13821,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="343" s="9" customFormat="1" spans="1:7">
+    <row r="343" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A343" s="13" t="s">
         <v>703</v>
       </c>
@@ -13839,7 +13842,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="344" s="9" customFormat="1" spans="1:7">
+    <row r="344" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A344" s="13" t="s">
         <v>706</v>
       </c>
@@ -13860,7 +13863,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="345" s="9" customFormat="1" spans="1:7">
+    <row r="345" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A345" s="13" t="s">
         <v>709</v>
       </c>
@@ -13881,7 +13884,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="346" s="9" customFormat="1" spans="1:7">
+    <row r="346" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A346" s="13" t="s">
         <v>711</v>
       </c>
@@ -13902,7 +13905,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="347" s="9" customFormat="1" spans="1:7">
+    <row r="347" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A347" s="13" t="s">
         <v>714</v>
       </c>
@@ -13923,7 +13926,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="348" s="9" customFormat="1" spans="1:7">
+    <row r="348" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A348" s="13" t="s">
         <v>716</v>
       </c>
@@ -13940,7 +13943,7 @@
       </c>
       <c r="G348" s="1"/>
     </row>
-    <row r="349" s="9" customFormat="1" spans="1:7">
+    <row r="349" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A349" s="13" t="s">
         <v>719</v>
       </c>
@@ -13959,7 +13962,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="350" s="9" customFormat="1" spans="1:7">
+    <row r="350" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A350" s="13" t="s">
         <v>721</v>
       </c>
@@ -13976,7 +13979,7 @@
       </c>
       <c r="G350" s="1"/>
     </row>
-    <row r="351" s="9" customFormat="1" spans="1:7">
+    <row r="351" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A351" s="13" t="s">
         <v>722</v>
       </c>
@@ -13993,7 +13996,7 @@
       </c>
       <c r="G351" s="1"/>
     </row>
-    <row r="352" s="9" customFormat="1" spans="1:7">
+    <row r="352" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A352" s="13" t="s">
         <v>723</v>
       </c>
@@ -14010,7 +14013,7 @@
       </c>
       <c r="G352" s="1"/>
     </row>
-    <row r="353" s="9" customFormat="1" spans="1:7">
+    <row r="353" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A353" s="13" t="s">
         <v>724</v>
       </c>
@@ -14027,7 +14030,7 @@
       </c>
       <c r="G353" s="1"/>
     </row>
-    <row r="354" s="9" customFormat="1" spans="1:7">
+    <row r="354" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A354" s="13" t="s">
         <v>725</v>
       </c>
@@ -14044,7 +14047,7 @@
       </c>
       <c r="G354" s="1"/>
     </row>
-    <row r="355" s="9" customFormat="1" spans="1:7">
+    <row r="355" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A355" s="13" t="s">
         <v>726</v>
       </c>
@@ -14061,7 +14064,7 @@
       </c>
       <c r="G355" s="1"/>
     </row>
-    <row r="356" s="9" customFormat="1" spans="1:7">
+    <row r="356" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A356" s="13" t="s">
         <v>727</v>
       </c>
@@ -14078,7 +14081,7 @@
       </c>
       <c r="G356" s="1"/>
     </row>
-    <row r="357" s="9" customFormat="1" spans="1:7">
+    <row r="357" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A357" s="13" t="s">
         <v>728</v>
       </c>
@@ -14095,7 +14098,7 @@
       </c>
       <c r="G357" s="1"/>
     </row>
-    <row r="358" s="9" customFormat="1" spans="1:7">
+    <row r="358" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A358" s="13" t="s">
         <v>729</v>
       </c>
@@ -14112,7 +14115,7 @@
       </c>
       <c r="G358" s="1"/>
     </row>
-    <row r="359" s="9" customFormat="1" spans="1:7">
+    <row r="359" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A359" s="13" t="s">
         <v>730</v>
       </c>
@@ -14129,7 +14132,7 @@
       </c>
       <c r="G359" s="1"/>
     </row>
-    <row r="360" s="9" customFormat="1" spans="1:7">
+    <row r="360" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A360" s="13" t="s">
         <v>731</v>
       </c>
@@ -14146,7 +14149,7 @@
       </c>
       <c r="G360" s="1"/>
     </row>
-    <row r="361" s="9" customFormat="1" spans="1:7">
+    <row r="361" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A361" s="13" t="s">
         <v>732</v>
       </c>
@@ -14163,7 +14166,7 @@
       </c>
       <c r="G361" s="1"/>
     </row>
-    <row r="362" s="9" customFormat="1" spans="1:7">
+    <row r="362" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A362" s="13" t="s">
         <v>733</v>
       </c>
@@ -14180,7 +14183,7 @@
       </c>
       <c r="G362" s="1"/>
     </row>
-    <row r="363" s="9" customFormat="1" spans="1:7">
+    <row r="363" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A363" s="13" t="s">
         <v>734</v>
       </c>
@@ -14197,7 +14200,7 @@
       </c>
       <c r="G363" s="1"/>
     </row>
-    <row r="364" s="9" customFormat="1" spans="1:7">
+    <row r="364" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A364" s="13" t="s">
         <v>735</v>
       </c>
@@ -14214,7 +14217,7 @@
       </c>
       <c r="G364" s="1"/>
     </row>
-    <row r="365" s="9" customFormat="1" spans="1:7">
+    <row r="365" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A365" s="13" t="s">
         <v>737</v>
       </c>
@@ -14231,7 +14234,7 @@
       </c>
       <c r="G365" s="1"/>
     </row>
-    <row r="366" s="9" customFormat="1" spans="1:7">
+    <row r="366" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A366" s="13" t="s">
         <v>738</v>
       </c>
@@ -14248,7 +14251,7 @@
       </c>
       <c r="G366" s="1"/>
     </row>
-    <row r="367" s="9" customFormat="1" spans="1:7">
+    <row r="367" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A367" s="13" t="s">
         <v>739</v>
       </c>
@@ -14265,7 +14268,7 @@
       </c>
       <c r="G367" s="1"/>
     </row>
-    <row r="368" s="9" customFormat="1" spans="1:7">
+    <row r="368" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A368" s="13" t="s">
         <v>740</v>
       </c>
@@ -14282,7 +14285,7 @@
       </c>
       <c r="G368" s="1"/>
     </row>
-    <row r="369" s="9" customFormat="1" spans="1:7">
+    <row r="369" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A369" s="13" t="s">
         <v>741</v>
       </c>
@@ -14299,7 +14302,7 @@
       </c>
       <c r="G369" s="1"/>
     </row>
-    <row r="370" s="9" customFormat="1" spans="1:7">
+    <row r="370" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A370" s="13" t="s">
         <v>742</v>
       </c>
@@ -14316,7 +14319,7 @@
       </c>
       <c r="G370" s="1"/>
     </row>
-    <row r="371" s="9" customFormat="1" spans="1:7">
+    <row r="371" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A371" s="13" t="s">
         <v>743</v>
       </c>
@@ -14333,7 +14336,7 @@
       </c>
       <c r="G371" s="1"/>
     </row>
-    <row r="372" s="9" customFormat="1" spans="1:7">
+    <row r="372" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A372" s="13" t="s">
         <v>744</v>
       </c>
@@ -14350,7 +14353,7 @@
       </c>
       <c r="G372" s="1"/>
     </row>
-    <row r="373" s="9" customFormat="1" spans="1:7">
+    <row r="373" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A373" s="13" t="s">
         <v>745</v>
       </c>
@@ -14367,7 +14370,7 @@
       </c>
       <c r="G373" s="1"/>
     </row>
-    <row r="374" s="9" customFormat="1" spans="1:7">
+    <row r="374" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A374" s="13" t="s">
         <v>746</v>
       </c>
@@ -14384,7 +14387,7 @@
       </c>
       <c r="G374" s="1"/>
     </row>
-    <row r="375" s="9" customFormat="1" spans="1:7">
+    <row r="375" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A375" s="13" t="s">
         <v>747</v>
       </c>
@@ -14401,7 +14404,7 @@
       </c>
       <c r="G375" s="1"/>
     </row>
-    <row r="376" s="9" customFormat="1" spans="1:7">
+    <row r="376" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A376" s="13" t="s">
         <v>748</v>
       </c>
@@ -14418,7 +14421,7 @@
       </c>
       <c r="G376" s="1"/>
     </row>
-    <row r="377" s="9" customFormat="1" spans="1:7">
+    <row r="377" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A377" s="13" t="s">
         <v>749</v>
       </c>
@@ -14435,7 +14438,7 @@
       </c>
       <c r="G377" s="1"/>
     </row>
-    <row r="378" s="9" customFormat="1" spans="1:7">
+    <row r="378" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A378" s="13" t="s">
         <v>750</v>
       </c>
@@ -14452,7 +14455,7 @@
       </c>
       <c r="G378" s="1"/>
     </row>
-    <row r="379" s="9" customFormat="1" spans="1:7">
+    <row r="379" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A379" s="13" t="s">
         <v>751</v>
       </c>
@@ -14471,7 +14474,7 @@
       </c>
       <c r="G379" s="1"/>
     </row>
-    <row r="380" s="9" customFormat="1" spans="1:7">
+    <row r="380" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A380" s="13" t="s">
         <v>754</v>
       </c>
@@ -14490,7 +14493,7 @@
       </c>
       <c r="G380" s="1"/>
     </row>
-    <row r="381" s="9" customFormat="1" spans="1:7">
+    <row r="381" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A381" s="13" t="s">
         <v>756</v>
       </c>
@@ -14509,7 +14512,7 @@
       </c>
       <c r="G381" s="1"/>
     </row>
-    <row r="382" s="9" customFormat="1" spans="1:7">
+    <row r="382" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A382" s="13" t="s">
         <v>758</v>
       </c>
@@ -14528,7 +14531,7 @@
       </c>
       <c r="G382" s="1"/>
     </row>
-    <row r="383" s="9" customFormat="1" spans="1:7">
+    <row r="383" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A383" s="13" t="s">
         <v>760</v>
       </c>
@@ -14547,7 +14550,7 @@
       </c>
       <c r="G383" s="1"/>
     </row>
-    <row r="384" s="9" customFormat="1" spans="1:7">
+    <row r="384" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A384" s="13" t="s">
         <v>763</v>
       </c>
@@ -14566,7 +14569,7 @@
       </c>
       <c r="G384" s="1"/>
     </row>
-    <row r="385" s="9" customFormat="1" spans="1:7">
+    <row r="385" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A385" s="13" t="s">
         <v>765</v>
       </c>
@@ -14585,7 +14588,7 @@
       </c>
       <c r="G385" s="1"/>
     </row>
-    <row r="386" s="9" customFormat="1" spans="1:7">
+    <row r="386" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A386" s="13" t="s">
         <v>767</v>
       </c>
@@ -14604,7 +14607,7 @@
       </c>
       <c r="G386" s="1"/>
     </row>
-    <row r="387" s="9" customFormat="1" spans="1:7">
+    <row r="387" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A387" s="13" t="s">
         <v>769</v>
       </c>
@@ -14623,7 +14626,7 @@
       </c>
       <c r="G387" s="1"/>
     </row>
-    <row r="388" s="9" customFormat="1" spans="1:7">
+    <row r="388" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A388" s="13" t="s">
         <v>771</v>
       </c>
@@ -14642,7 +14645,7 @@
       </c>
       <c r="G388" s="1"/>
     </row>
-    <row r="389" s="9" customFormat="1" spans="1:7">
+    <row r="389" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A389" s="13" t="s">
         <v>773</v>
       </c>
@@ -14661,7 +14664,7 @@
       </c>
       <c r="G389" s="1"/>
     </row>
-    <row r="390" s="9" customFormat="1" spans="1:7">
+    <row r="390" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A390" s="13" t="s">
         <v>775</v>
       </c>
@@ -14680,7 +14683,7 @@
       </c>
       <c r="G390" s="1"/>
     </row>
-    <row r="391" s="9" customFormat="1" spans="1:7">
+    <row r="391" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A391" s="13" t="s">
         <v>777</v>
       </c>
@@ -14699,7 +14702,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="392" s="9" customFormat="1" spans="1:7">
+    <row r="392" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A392" s="13" t="s">
         <v>779</v>
       </c>
@@ -14718,7 +14721,7 @@
       </c>
       <c r="G392" s="1"/>
     </row>
-    <row r="393" s="9" customFormat="1" spans="1:7">
+    <row r="393" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A393" s="13" t="s">
         <v>781</v>
       </c>
@@ -14735,7 +14738,7 @@
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
     </row>
-    <row r="394" s="9" customFormat="1" spans="1:7">
+    <row r="394" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A394" s="13" t="s">
         <v>783</v>
       </c>
@@ -14754,7 +14757,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="395" s="9" customFormat="1" spans="1:7">
+    <row r="395" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A395" s="13" t="s">
         <v>786</v>
       </c>
@@ -14773,7 +14776,7 @@
       </c>
       <c r="G395" s="1"/>
     </row>
-    <row r="396" s="9" customFormat="1" spans="1:7">
+    <row r="396" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A396" s="13" t="s">
         <v>788</v>
       </c>
@@ -14792,7 +14795,7 @@
       </c>
       <c r="G396" s="1"/>
     </row>
-    <row r="397" s="9" customFormat="1" spans="1:7">
+    <row r="397" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A397" s="13" t="s">
         <v>790</v>
       </c>
@@ -14811,7 +14814,7 @@
       </c>
       <c r="G397" s="1"/>
     </row>
-    <row r="398" s="9" customFormat="1" spans="1:7">
+    <row r="398" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A398" s="13" t="s">
         <v>792</v>
       </c>
@@ -14832,7 +14835,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="399" s="9" customFormat="1" spans="1:7">
+    <row r="399" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A399" s="13" t="s">
         <v>795</v>
       </c>
@@ -14849,7 +14852,7 @@
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
     </row>
-    <row r="400" s="9" customFormat="1" spans="1:7">
+    <row r="400" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A400" s="13" t="s">
         <v>797</v>
       </c>
@@ -14868,7 +14871,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="401" s="9" customFormat="1" spans="1:7">
+    <row r="401" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A401" s="13" t="s">
         <v>800</v>
       </c>
@@ -14887,7 +14890,7 @@
       </c>
       <c r="G401" s="1"/>
     </row>
-    <row r="402" s="9" customFormat="1" spans="1:7">
+    <row r="402" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A402" s="13" t="s">
         <v>803</v>
       </c>
@@ -14906,7 +14909,7 @@
       </c>
       <c r="G402" s="1"/>
     </row>
-    <row r="403" s="9" customFormat="1" spans="1:7">
+    <row r="403" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A403" s="13" t="s">
         <v>805</v>
       </c>
@@ -14925,7 +14928,7 @@
       </c>
       <c r="G403" s="1"/>
     </row>
-    <row r="404" s="9" customFormat="1" spans="1:7">
+    <row r="404" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A404" s="13" t="s">
         <v>807</v>
       </c>
@@ -14946,7 +14949,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="405" s="9" customFormat="1" spans="1:7">
+    <row r="405" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A405" s="13" t="s">
         <v>810</v>
       </c>
@@ -14967,7 +14970,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="406" s="9" customFormat="1" spans="1:7">
+    <row r="406" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A406" s="13" t="s">
         <v>812</v>
       </c>
@@ -14986,7 +14989,7 @@
       <c r="F406" s="1"/>
       <c r="G406" s="1"/>
     </row>
-    <row r="407" s="9" customFormat="1" spans="1:7">
+    <row r="407" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A407" s="13" t="s">
         <v>816</v>
       </c>
@@ -15007,7 +15010,7 @@
       </c>
       <c r="G407" s="1"/>
     </row>
-    <row r="408" s="9" customFormat="1" spans="1:7">
+    <row r="408" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A408" s="13" t="s">
         <v>819</v>
       </c>
@@ -15030,7 +15033,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="409" s="9" customFormat="1" spans="1:7">
+    <row r="409" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A409" s="13" t="s">
         <v>823</v>
       </c>
@@ -15051,7 +15054,7 @@
       </c>
       <c r="G409" s="1"/>
     </row>
-    <row r="410" s="9" customFormat="1" spans="1:7">
+    <row r="410" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A410" s="13" t="s">
         <v>826</v>
       </c>
@@ -15072,7 +15075,7 @@
       </c>
       <c r="G410" s="1"/>
     </row>
-    <row r="411" s="9" customFormat="1" spans="1:7">
+    <row r="411" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A411" s="13" t="s">
         <v>829</v>
       </c>
@@ -15095,7 +15098,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="412" s="9" customFormat="1" spans="1:7">
+    <row r="412" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A412" s="13" t="s">
         <v>833</v>
       </c>
@@ -15116,7 +15119,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="413" s="9" customFormat="1" spans="1:7">
+    <row r="413" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A413" s="13" t="s">
         <v>837</v>
       </c>
@@ -15133,7 +15136,7 @@
       <c r="F413" s="1"/>
       <c r="G413" s="1"/>
     </row>
-    <row r="414" s="9" customFormat="1" spans="1:7">
+    <row r="414" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A414" s="13" t="s">
         <v>839</v>
       </c>
@@ -15152,7 +15155,7 @@
       </c>
       <c r="G414" s="1"/>
     </row>
-    <row r="415" s="9" customFormat="1" spans="1:7">
+    <row r="415" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A415" s="13" t="s">
         <v>842</v>
       </c>
@@ -15169,7 +15172,7 @@
       </c>
       <c r="G415" s="1"/>
     </row>
-    <row r="416" s="9" customFormat="1" spans="1:7">
+    <row r="416" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A416" s="13" t="s">
         <v>844</v>
       </c>
@@ -15186,7 +15189,7 @@
       </c>
       <c r="G416" s="1"/>
     </row>
-    <row r="417" s="9" customFormat="1" spans="1:7">
+    <row r="417" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A417" s="13" t="s">
         <v>845</v>
       </c>
@@ -15205,7 +15208,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="418" s="9" customFormat="1" spans="1:7">
+    <row r="418" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A418" s="13" t="s">
         <v>847</v>
       </c>
@@ -15224,7 +15227,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="419" s="9" customFormat="1" spans="1:7">
+    <row r="419" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A419" s="13" t="s">
         <v>849</v>
       </c>
@@ -15241,7 +15244,7 @@
       </c>
       <c r="G419" s="1"/>
     </row>
-    <row r="420" s="9" customFormat="1" spans="1:7">
+    <row r="420" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A420" s="13" t="s">
         <v>851</v>
       </c>
@@ -15260,7 +15263,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="421" s="9" customFormat="1" spans="1:7">
+    <row r="421" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A421" s="13" t="s">
         <v>854</v>
       </c>
@@ -15279,7 +15282,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="422" s="9" customFormat="1" spans="1:7">
+    <row r="422" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A422" s="13" t="s">
         <v>856</v>
       </c>
@@ -15298,7 +15301,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="423" s="9" customFormat="1" spans="1:7">
+    <row r="423" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A423" s="13" t="s">
         <v>859</v>
       </c>
@@ -15317,7 +15320,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="424" s="9" customFormat="1" spans="1:7">
+    <row r="424" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A424" s="20" t="s">
         <v>861</v>
       </c>
@@ -15334,7 +15337,7 @@
       </c>
       <c r="G424" s="19"/>
     </row>
-    <row r="425" s="9" customFormat="1" spans="1:7">
+    <row r="425" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A425" s="20" t="s">
         <v>863</v>
       </c>
@@ -15355,7 +15358,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="426" s="9" customFormat="1" spans="1:7">
+    <row r="426" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A426" s="20" t="s">
         <v>866</v>
       </c>
@@ -15372,7 +15375,7 @@
       </c>
       <c r="G426" s="19"/>
     </row>
-    <row r="427" s="9" customFormat="1" spans="1:7">
+    <row r="427" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A427" s="20" t="s">
         <v>867</v>
       </c>
@@ -15389,7 +15392,7 @@
       </c>
       <c r="G427" s="19"/>
     </row>
-    <row r="428" s="9" customFormat="1" spans="1:7">
+    <row r="428" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A428" s="20" t="s">
         <v>870</v>
       </c>
@@ -15406,7 +15409,7 @@
       </c>
       <c r="G428" s="19"/>
     </row>
-    <row r="429" s="9" customFormat="1" spans="1:7">
+    <row r="429" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A429" s="20" t="s">
         <v>873</v>
       </c>
@@ -15423,7 +15426,7 @@
       </c>
       <c r="G429" s="19"/>
     </row>
-    <row r="430" s="9" customFormat="1" spans="1:7">
+    <row r="430" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A430" s="20" t="s">
         <v>875</v>
       </c>
@@ -15440,7 +15443,7 @@
       </c>
       <c r="G430" s="19"/>
     </row>
-    <row r="431" s="9" customFormat="1" spans="1:7">
+    <row r="431" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A431" s="20" t="s">
         <v>877</v>
       </c>
@@ -15457,7 +15460,7 @@
       </c>
       <c r="G431" s="19"/>
     </row>
-    <row r="432" s="9" customFormat="1" spans="1:7">
+    <row r="432" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A432" s="20" t="s">
         <v>879</v>
       </c>
@@ -15476,7 +15479,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="433" s="9" customFormat="1" spans="1:7">
+    <row r="433" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A433" s="20" t="s">
         <v>883</v>
       </c>
@@ -15493,7 +15496,7 @@
       </c>
       <c r="G433" s="19"/>
     </row>
-    <row r="434" s="9" customFormat="1" spans="1:7">
+    <row r="434" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A434" s="20" t="s">
         <v>885</v>
       </c>
@@ -15510,7 +15513,7 @@
       </c>
       <c r="G434" s="19"/>
     </row>
-    <row r="435" s="9" customFormat="1" spans="1:7">
+    <row r="435" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A435" s="20" t="s">
         <v>887</v>
       </c>
@@ -15531,7 +15534,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="436" s="9" customFormat="1" spans="1:7">
+    <row r="436" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A436" s="20" t="s">
         <v>890</v>
       </c>
@@ -15548,7 +15551,7 @@
       </c>
       <c r="G436" s="19"/>
     </row>
-    <row r="437" s="9" customFormat="1" spans="1:7">
+    <row r="437" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A437" s="20" t="s">
         <v>891</v>
       </c>
@@ -15565,7 +15568,7 @@
       </c>
       <c r="G437" s="19"/>
     </row>
-    <row r="438" s="9" customFormat="1" spans="1:7">
+    <row r="438" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A438" s="20" t="s">
         <v>893</v>
       </c>
@@ -15582,7 +15585,7 @@
       </c>
       <c r="G438" s="19"/>
     </row>
-    <row r="439" s="9" customFormat="1" spans="1:7">
+    <row r="439" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A439" s="20" t="s">
         <v>896</v>
       </c>
@@ -15599,7 +15602,7 @@
       </c>
       <c r="G439" s="19"/>
     </row>
-    <row r="440" s="9" customFormat="1" spans="1:7">
+    <row r="440" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A440" s="20" t="s">
         <v>898</v>
       </c>
@@ -15616,7 +15619,7 @@
       </c>
       <c r="G440" s="19"/>
     </row>
-    <row r="441" s="9" customFormat="1" spans="1:7">
+    <row r="441" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A441" s="20" t="s">
         <v>900</v>
       </c>
@@ -15633,7 +15636,7 @@
       </c>
       <c r="G441" s="19"/>
     </row>
-    <row r="442" s="9" customFormat="1" spans="1:7">
+    <row r="442" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A442" s="20" t="s">
         <v>902</v>
       </c>
@@ -15650,7 +15653,7 @@
       </c>
       <c r="G442" s="19"/>
     </row>
-    <row r="443" s="9" customFormat="1" spans="1:7">
+    <row r="443" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A443" s="20" t="s">
         <v>905</v>
       </c>
@@ -15667,7 +15670,7 @@
       </c>
       <c r="G443" s="19"/>
     </row>
-    <row r="444" s="9" customFormat="1" spans="1:7">
+    <row r="444" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A444" s="20" t="s">
         <v>908</v>
       </c>
@@ -15684,7 +15687,7 @@
       </c>
       <c r="G444" s="19"/>
     </row>
-    <row r="445" s="9" customFormat="1" spans="1:7">
+    <row r="445" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A445" s="20" t="s">
         <v>910</v>
       </c>
@@ -15701,7 +15704,7 @@
       </c>
       <c r="G445" s="19"/>
     </row>
-    <row r="446" s="9" customFormat="1" spans="1:7">
+    <row r="446" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A446" s="20" t="s">
         <v>912</v>
       </c>
@@ -15718,7 +15721,7 @@
       </c>
       <c r="G446" s="19"/>
     </row>
-    <row r="447" s="9" customFormat="1" spans="1:7">
+    <row r="447" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A447" s="20" t="s">
         <v>914</v>
       </c>
@@ -15735,7 +15738,7 @@
       </c>
       <c r="G447" s="19"/>
     </row>
-    <row r="448" s="9" customFormat="1" spans="1:7">
+    <row r="448" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A448" s="20" t="s">
         <v>917</v>
       </c>
@@ -15752,7 +15755,7 @@
       </c>
       <c r="G448" s="19"/>
     </row>
-    <row r="449" s="9" customFormat="1" spans="1:7">
+    <row r="449" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A449" s="20" t="s">
         <v>919</v>
       </c>
@@ -15769,7 +15772,7 @@
       </c>
       <c r="G449" s="19"/>
     </row>
-    <row r="450" s="9" customFormat="1" spans="1:7">
+    <row r="450" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A450" s="20" t="s">
         <v>921</v>
       </c>
@@ -15786,7 +15789,7 @@
       </c>
       <c r="G450" s="19"/>
     </row>
-    <row r="451" s="9" customFormat="1" spans="1:7">
+    <row r="451" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A451" s="20" t="s">
         <v>923</v>
       </c>
@@ -15805,7 +15808,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="452" s="9" customFormat="1" spans="1:7">
+    <row r="452" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A452" s="20" t="s">
         <v>925</v>
       </c>
@@ -15824,7 +15827,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="453" s="9" customFormat="1" spans="1:7">
+    <row r="453" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A453" s="20" t="s">
         <v>926</v>
       </c>
@@ -15841,7 +15844,7 @@
       </c>
       <c r="G453" s="19"/>
     </row>
-    <row r="454" s="9" customFormat="1" spans="1:7">
+    <row r="454" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A454" s="20" t="s">
         <v>928</v>
       </c>
@@ -15858,7 +15861,7 @@
       </c>
       <c r="G454" s="19"/>
     </row>
-    <row r="455" s="9" customFormat="1" spans="1:7">
+    <row r="455" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A455" s="20" t="s">
         <v>930</v>
       </c>
@@ -15877,7 +15880,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="456" s="9" customFormat="1" spans="1:7">
+    <row r="456" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A456" s="20" t="s">
         <v>933</v>
       </c>
@@ -15894,7 +15897,7 @@
       </c>
       <c r="G456" s="19"/>
     </row>
-    <row r="457" s="9" customFormat="1" spans="1:7">
+    <row r="457" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A457" s="20" t="s">
         <v>935</v>
       </c>
@@ -15911,7 +15914,7 @@
       </c>
       <c r="G457" s="19"/>
     </row>
-    <row r="458" s="9" customFormat="1" spans="1:7">
+    <row r="458" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A458" s="20" t="s">
         <v>937</v>
       </c>
@@ -15928,7 +15931,7 @@
       </c>
       <c r="G458" s="19"/>
     </row>
-    <row r="459" s="9" customFormat="1" spans="1:7">
+    <row r="459" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A459" s="20" t="s">
         <v>939</v>
       </c>
@@ -15947,7 +15950,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="460" s="9" customFormat="1" spans="1:7">
+    <row r="460" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A460" s="20" t="s">
         <v>942</v>
       </c>
@@ -15964,7 +15967,7 @@
       </c>
       <c r="G460" s="19"/>
     </row>
-    <row r="461" s="9" customFormat="1" spans="1:7">
+    <row r="461" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A461" s="20" t="s">
         <v>944</v>
       </c>
@@ -15981,7 +15984,7 @@
       </c>
       <c r="G461" s="19"/>
     </row>
-    <row r="462" s="9" customFormat="1" spans="1:7">
+    <row r="462" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A462" s="20" t="s">
         <v>947</v>
       </c>
@@ -15998,7 +16001,7 @@
       </c>
       <c r="G462" s="19"/>
     </row>
-    <row r="463" s="9" customFormat="1" spans="1:7">
+    <row r="463" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A463" s="20" t="s">
         <v>949</v>
       </c>
@@ -16015,7 +16018,7 @@
       </c>
       <c r="G463" s="19"/>
     </row>
-    <row r="464" s="9" customFormat="1" spans="1:7">
+    <row r="464" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A464" s="20" t="s">
         <v>951</v>
       </c>
@@ -16032,7 +16035,7 @@
       </c>
       <c r="G464" s="19"/>
     </row>
-    <row r="465" s="9" customFormat="1" spans="1:7">
+    <row r="465" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A465" s="20" t="s">
         <v>953</v>
       </c>
@@ -16049,7 +16052,7 @@
       </c>
       <c r="G465" s="19"/>
     </row>
-    <row r="466" s="9" customFormat="1" spans="1:7">
+    <row r="466" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A466" s="20" t="s">
         <v>955</v>
       </c>
@@ -16066,7 +16069,7 @@
       </c>
       <c r="G466" s="19"/>
     </row>
-    <row r="467" s="9" customFormat="1" spans="1:7">
+    <row r="467" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A467" s="20" t="s">
         <v>957</v>
       </c>
@@ -16083,7 +16086,7 @@
       </c>
       <c r="G467" s="19"/>
     </row>
-    <row r="468" s="9" customFormat="1" spans="1:7">
+    <row r="468" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A468" s="20" t="s">
         <v>959</v>
       </c>
@@ -16102,7 +16105,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="469" s="9" customFormat="1" spans="1:7">
+    <row r="469" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A469" s="20" t="s">
         <v>962</v>
       </c>
@@ -16119,7 +16122,7 @@
       </c>
       <c r="G469" s="19"/>
     </row>
-    <row r="470" s="9" customFormat="1" spans="1:7">
+    <row r="470" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A470" s="20" t="s">
         <v>964</v>
       </c>
@@ -16138,7 +16141,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="471" s="9" customFormat="1" spans="1:7">
+    <row r="471" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A471" s="20" t="s">
         <v>967</v>
       </c>
@@ -16155,7 +16158,7 @@
       </c>
       <c r="G471" s="19"/>
     </row>
-    <row r="472" s="9" customFormat="1" spans="1:7">
+    <row r="472" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A472" s="20" t="s">
         <v>969</v>
       </c>
@@ -16172,7 +16175,7 @@
       </c>
       <c r="G472" s="19"/>
     </row>
-    <row r="473" s="9" customFormat="1" spans="1:7">
+    <row r="473" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A473" s="20" t="s">
         <v>971</v>
       </c>
@@ -16189,7 +16192,7 @@
       </c>
       <c r="G473" s="19"/>
     </row>
-    <row r="474" s="9" customFormat="1" spans="1:7">
+    <row r="474" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A474" s="20" t="s">
         <v>973</v>
       </c>
@@ -16206,7 +16209,7 @@
       </c>
       <c r="G474" s="19"/>
     </row>
-    <row r="475" s="9" customFormat="1" spans="1:7">
+    <row r="475" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A475" s="20" t="s">
         <v>975</v>
       </c>
@@ -16223,7 +16226,7 @@
       </c>
       <c r="G475" s="19"/>
     </row>
-    <row r="476" s="9" customFormat="1" spans="1:7">
+    <row r="476" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A476" s="20" t="s">
         <v>977</v>
       </c>
@@ -16240,7 +16243,7 @@
       </c>
       <c r="G476" s="19"/>
     </row>
-    <row r="477" s="9" customFormat="1" spans="1:7">
+    <row r="477" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A477" s="20" t="s">
         <v>979</v>
       </c>
@@ -16257,7 +16260,7 @@
       </c>
       <c r="G477" s="19"/>
     </row>
-    <row r="478" s="9" customFormat="1" spans="1:7">
+    <row r="478" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A478" s="20" t="s">
         <v>981</v>
       </c>
@@ -16274,7 +16277,7 @@
       </c>
       <c r="G478" s="19"/>
     </row>
-    <row r="479" s="9" customFormat="1" spans="1:7">
+    <row r="479" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A479" s="20" t="s">
         <v>982</v>
       </c>
@@ -16291,7 +16294,7 @@
       </c>
       <c r="G479" s="19"/>
     </row>
-    <row r="480" s="9" customFormat="1" spans="1:7">
+    <row r="480" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A480" s="20" t="s">
         <v>983</v>
       </c>
@@ -16308,7 +16311,7 @@
       </c>
       <c r="G480" s="19"/>
     </row>
-    <row r="481" s="9" customFormat="1" spans="1:7">
+    <row r="481" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A481" s="20" t="s">
         <v>984</v>
       </c>
@@ -16325,7 +16328,7 @@
       </c>
       <c r="G481" s="19"/>
     </row>
-    <row r="482" s="9" customFormat="1" spans="1:7">
+    <row r="482" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A482" s="20" t="s">
         <v>985</v>
       </c>
@@ -16342,7 +16345,7 @@
       </c>
       <c r="G482" s="19"/>
     </row>
-    <row r="483" s="9" customFormat="1" spans="1:7">
+    <row r="483" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A483" s="20" t="s">
         <v>987</v>
       </c>
@@ -16359,7 +16362,7 @@
       </c>
       <c r="G483" s="19"/>
     </row>
-    <row r="484" s="9" customFormat="1" spans="1:7">
+    <row r="484" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A484" s="20" t="s">
         <v>988</v>
       </c>
@@ -16376,7 +16379,7 @@
       </c>
       <c r="G484" s="19"/>
     </row>
-    <row r="485" s="9" customFormat="1" spans="1:7">
+    <row r="485" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A485" s="20" t="s">
         <v>989</v>
       </c>
@@ -16395,7 +16398,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="486" s="9" customFormat="1" spans="1:7">
+    <row r="486" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A486" s="20" t="s">
         <v>991</v>
       </c>
@@ -16414,7 +16417,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="487" s="9" customFormat="1" spans="1:7">
+    <row r="487" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A487" s="20" t="s">
         <v>993</v>
       </c>
@@ -16433,7 +16436,7 @@
       </c>
       <c r="G487" s="19"/>
     </row>
-    <row r="488" s="9" customFormat="1" spans="1:7">
+    <row r="488" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A488" s="20" t="s">
         <v>995</v>
       </c>
@@ -16452,7 +16455,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="489" s="9" customFormat="1" spans="1:7">
+    <row r="489" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A489" s="20" t="s">
         <v>998</v>
       </c>
@@ -16471,7 +16474,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="490" s="9" customFormat="1" spans="1:7">
+    <row r="490" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A490" s="20" t="s">
         <v>1000</v>
       </c>
@@ -16488,7 +16491,7 @@
       </c>
       <c r="G490" s="19"/>
     </row>
-    <row r="491" s="9" customFormat="1" spans="1:7">
+    <row r="491" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A491" s="20" t="s">
         <v>1002</v>
       </c>
@@ -16505,7 +16508,7 @@
       </c>
       <c r="G491" s="19"/>
     </row>
-    <row r="492" s="9" customFormat="1" spans="1:7">
+    <row r="492" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A492" s="20" t="s">
         <v>1003</v>
       </c>
@@ -16522,7 +16525,7 @@
       </c>
       <c r="G492" s="19"/>
     </row>
-    <row r="493" s="9" customFormat="1" spans="1:7">
+    <row r="493" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A493" s="20" t="s">
         <v>1004</v>
       </c>
@@ -16539,7 +16542,7 @@
       </c>
       <c r="G493" s="19"/>
     </row>
-    <row r="494" s="9" customFormat="1" spans="1:7">
+    <row r="494" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A494" s="20" t="s">
         <v>1005</v>
       </c>
@@ -16556,7 +16559,7 @@
       </c>
       <c r="G494" s="19"/>
     </row>
-    <row r="495" s="9" customFormat="1" spans="1:7">
+    <row r="495" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A495" s="20" t="s">
         <v>1006</v>
       </c>
@@ -16575,7 +16578,7 @@
       </c>
       <c r="G495" s="19"/>
     </row>
-    <row r="496" s="9" customFormat="1" spans="1:7">
+    <row r="496" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A496" s="20" t="s">
         <v>1008</v>
       </c>
@@ -16592,7 +16595,7 @@
       </c>
       <c r="G496" s="19"/>
     </row>
-    <row r="497" s="9" customFormat="1" spans="1:7">
+    <row r="497" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A497" s="20" t="s">
         <v>1009</v>
       </c>
@@ -16609,7 +16612,7 @@
       </c>
       <c r="G497" s="19"/>
     </row>
-    <row r="498" s="9" customFormat="1" spans="1:7">
+    <row r="498" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A498" s="20" t="s">
         <v>1010</v>
       </c>
@@ -16628,7 +16631,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="499" s="9" customFormat="1" spans="1:7">
+    <row r="499" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A499" s="20" t="s">
         <v>1012</v>
       </c>
@@ -16647,7 +16650,7 @@
       </c>
       <c r="G499" s="19"/>
     </row>
-    <row r="500" s="9" customFormat="1" spans="1:7">
+    <row r="500" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A500" s="20" t="s">
         <v>1014</v>
       </c>
@@ -16664,7 +16667,7 @@
       </c>
       <c r="G500" s="19"/>
     </row>
-    <row r="501" s="9" customFormat="1" spans="1:7">
+    <row r="501" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A501" s="20" t="s">
         <v>1015</v>
       </c>
@@ -16681,7 +16684,7 @@
       </c>
       <c r="G501" s="19"/>
     </row>
-    <row r="502" s="9" customFormat="1" spans="1:7">
+    <row r="502" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A502" s="20" t="s">
         <v>1016</v>
       </c>
@@ -16698,7 +16701,7 @@
       </c>
       <c r="G502" s="19"/>
     </row>
-    <row r="503" s="9" customFormat="1" spans="1:7">
+    <row r="503" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A503" s="20" t="s">
         <v>1017</v>
       </c>
@@ -16715,7 +16718,7 @@
       </c>
       <c r="G503" s="19"/>
     </row>
-    <row r="504" s="9" customFormat="1" spans="1:7">
+    <row r="504" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A504" s="20" t="s">
         <v>1018</v>
       </c>
@@ -16732,7 +16735,7 @@
       </c>
       <c r="G504" s="19"/>
     </row>
-    <row r="505" s="9" customFormat="1" spans="1:7">
+    <row r="505" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A505" s="20" t="s">
         <v>1019</v>
       </c>
@@ -16751,7 +16754,7 @@
       </c>
       <c r="G505" s="19"/>
     </row>
-    <row r="506" s="9" customFormat="1" spans="1:7">
+    <row r="506" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A506" s="20" t="s">
         <v>1021</v>
       </c>
@@ -16768,7 +16771,7 @@
       </c>
       <c r="G506" s="19"/>
     </row>
-    <row r="507" s="9" customFormat="1" spans="1:7">
+    <row r="507" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A507" s="20" t="s">
         <v>1022</v>
       </c>
@@ -16785,7 +16788,7 @@
       </c>
       <c r="G507" s="19"/>
     </row>
-    <row r="508" s="9" customFormat="1" spans="1:7">
+    <row r="508" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A508" s="20" t="s">
         <v>1023</v>
       </c>
@@ -16804,7 +16807,7 @@
       </c>
       <c r="G508" s="19"/>
     </row>
-    <row r="509" s="9" customFormat="1" spans="1:7">
+    <row r="509" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A509" s="20" t="s">
         <v>1025</v>
       </c>
@@ -16823,7 +16826,7 @@
       </c>
       <c r="G509" s="19"/>
     </row>
-    <row r="510" s="9" customFormat="1" spans="1:7">
+    <row r="510" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A510" s="20" t="s">
         <v>1026</v>
       </c>
@@ -16844,7 +16847,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="511" s="9" customFormat="1" spans="1:7">
+    <row r="511" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A511" s="20" t="s">
         <v>1029</v>
       </c>
@@ -16863,7 +16866,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="512" s="9" customFormat="1" spans="1:7">
+    <row r="512" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A512" s="20" t="s">
         <v>1031</v>
       </c>
@@ -16882,7 +16885,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="513" s="9" customFormat="1" spans="1:7">
+    <row r="513" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A513" s="20" t="s">
         <v>1033</v>
       </c>
@@ -16899,7 +16902,7 @@
       </c>
       <c r="G513" s="19"/>
     </row>
-    <row r="514" s="9" customFormat="1" spans="1:7">
+    <row r="514" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A514" s="20" t="s">
         <v>1034</v>
       </c>
@@ -16916,7 +16919,7 @@
       </c>
       <c r="G514" s="19"/>
     </row>
-    <row r="515" s="9" customFormat="1" spans="1:7">
+    <row r="515" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A515" s="20" t="s">
         <v>1035</v>
       </c>
@@ -16933,7 +16936,7 @@
       </c>
       <c r="G515" s="19"/>
     </row>
-    <row r="516" s="9" customFormat="1" spans="1:7">
+    <row r="516" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A516" s="20" t="s">
         <v>1036</v>
       </c>
@@ -16950,7 +16953,7 @@
       </c>
       <c r="G516" s="19"/>
     </row>
-    <row r="517" s="9" customFormat="1" spans="1:7">
+    <row r="517" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A517" s="20" t="s">
         <v>1037</v>
       </c>
@@ -16967,7 +16970,7 @@
       </c>
       <c r="G517" s="19"/>
     </row>
-    <row r="518" s="9" customFormat="1" spans="1:7">
+    <row r="518" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A518" s="20" t="s">
         <v>1038</v>
       </c>
@@ -16984,7 +16987,7 @@
       </c>
       <c r="G518" s="19"/>
     </row>
-    <row r="519" s="9" customFormat="1" spans="1:7">
+    <row r="519" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A519" s="20" t="s">
         <v>1039</v>
       </c>
@@ -17001,7 +17004,7 @@
       </c>
       <c r="G519" s="19"/>
     </row>
-    <row r="520" s="9" customFormat="1" spans="1:7">
+    <row r="520" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A520" s="20" t="s">
         <v>1040</v>
       </c>
@@ -17018,7 +17021,7 @@
       </c>
       <c r="G520" s="19"/>
     </row>
-    <row r="521" s="9" customFormat="1" spans="1:7">
+    <row r="521" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A521" s="20" t="s">
         <v>1041</v>
       </c>
@@ -17035,7 +17038,7 @@
       </c>
       <c r="G521" s="19"/>
     </row>
-    <row r="522" s="9" customFormat="1" spans="1:7">
+    <row r="522" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A522" s="20" t="s">
         <v>1042</v>
       </c>
@@ -17052,7 +17055,7 @@
       </c>
       <c r="G522" s="19"/>
     </row>
-    <row r="523" s="9" customFormat="1" spans="1:7">
+    <row r="523" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A523" s="20" t="s">
         <v>1043</v>
       </c>
@@ -17069,7 +17072,7 @@
       </c>
       <c r="G523" s="19"/>
     </row>
-    <row r="524" s="9" customFormat="1" spans="1:7">
+    <row r="524" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A524" s="20" t="s">
         <v>1044</v>
       </c>
@@ -17086,7 +17089,7 @@
       </c>
       <c r="G524" s="19"/>
     </row>
-    <row r="525" s="9" customFormat="1" spans="1:7">
+    <row r="525" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A525" s="20" t="s">
         <v>1045</v>
       </c>
@@ -17103,7 +17106,7 @@
       </c>
       <c r="G525" s="19"/>
     </row>
-    <row r="526" s="9" customFormat="1" spans="1:7">
+    <row r="526" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A526" s="20" t="s">
         <v>1046</v>
       </c>
@@ -17120,7 +17123,7 @@
       </c>
       <c r="G526" s="19"/>
     </row>
-    <row r="527" s="9" customFormat="1" spans="1:7">
+    <row r="527" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A527" s="20" t="s">
         <v>1047</v>
       </c>
@@ -17137,7 +17140,7 @@
       </c>
       <c r="G527" s="19"/>
     </row>
-    <row r="528" s="9" customFormat="1" spans="1:7">
+    <row r="528" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A528" s="20" t="s">
         <v>1048</v>
       </c>
@@ -17154,7 +17157,7 @@
       </c>
       <c r="G528" s="19"/>
     </row>
-    <row r="529" s="9" customFormat="1" spans="1:7">
+    <row r="529" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A529" s="20" t="s">
         <v>1049</v>
       </c>
@@ -17171,7 +17174,7 @@
       </c>
       <c r="G529" s="19"/>
     </row>
-    <row r="530" s="9" customFormat="1" spans="1:7">
+    <row r="530" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A530" s="20" t="s">
         <v>1050</v>
       </c>
@@ -17188,7 +17191,7 @@
       </c>
       <c r="G530" s="19"/>
     </row>
-    <row r="531" s="9" customFormat="1" spans="1:7">
+    <row r="531" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A531" s="20" t="s">
         <v>1051</v>
       </c>
@@ -17205,7 +17208,7 @@
       </c>
       <c r="G531" s="19"/>
     </row>
-    <row r="532" s="9" customFormat="1" spans="1:7">
+    <row r="532" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A532" s="20" t="s">
         <v>1052</v>
       </c>
@@ -17222,7 +17225,7 @@
       </c>
       <c r="G532" s="19"/>
     </row>
-    <row r="533" s="9" customFormat="1" spans="1:7">
+    <row r="533" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A533" s="20" t="s">
         <v>1053</v>
       </c>
@@ -17241,7 +17244,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="534" s="9" customFormat="1" spans="1:7">
+    <row r="534" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A534" s="20" t="s">
         <v>1055</v>
       </c>
@@ -17258,7 +17261,7 @@
       </c>
       <c r="G534" s="19"/>
     </row>
-    <row r="535" s="9" customFormat="1" spans="1:7">
+    <row r="535" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A535" s="20" t="s">
         <v>1056</v>
       </c>
@@ -17275,7 +17278,7 @@
       </c>
       <c r="G535" s="19"/>
     </row>
-    <row r="536" s="9" customFormat="1" spans="1:7">
+    <row r="536" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A536" s="20" t="s">
         <v>1057</v>
       </c>
@@ -17292,7 +17295,7 @@
       </c>
       <c r="G536" s="19"/>
     </row>
-    <row r="537" s="9" customFormat="1" spans="1:7">
+    <row r="537" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A537" s="20" t="s">
         <v>1058</v>
       </c>
@@ -17309,7 +17312,7 @@
       </c>
       <c r="G537" s="19"/>
     </row>
-    <row r="538" s="9" customFormat="1" spans="1:7">
+    <row r="538" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A538" s="20" t="s">
         <v>1059</v>
       </c>
@@ -17326,7 +17329,7 @@
       </c>
       <c r="G538" s="19"/>
     </row>
-    <row r="539" s="9" customFormat="1" spans="1:7">
+    <row r="539" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A539" s="20" t="s">
         <v>1060</v>
       </c>
@@ -17347,7 +17350,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="540" s="9" customFormat="1" spans="1:7">
+    <row r="540" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A540" s="20" t="s">
         <v>1063</v>
       </c>
@@ -17368,7 +17371,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="541" s="9" customFormat="1" spans="1:7">
+    <row r="541" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A541" s="20" t="s">
         <v>1065</v>
       </c>
@@ -17387,7 +17390,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="542" s="9" customFormat="1" spans="1:7">
+    <row r="542" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A542" s="20" t="s">
         <v>1067</v>
       </c>
@@ -17404,7 +17407,7 @@
       </c>
       <c r="G542" s="19"/>
     </row>
-    <row r="543" s="9" customFormat="1" spans="1:7">
+    <row r="543" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A543" s="20" t="s">
         <v>1068</v>
       </c>
@@ -17423,7 +17426,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="544" s="9" customFormat="1" spans="1:7">
+    <row r="544" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A544" s="20" t="s">
         <v>1070</v>
       </c>
@@ -17444,7 +17447,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="545" s="9" customFormat="1" spans="1:7">
+    <row r="545" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A545" s="20" t="s">
         <v>1073</v>
       </c>
@@ -17463,7 +17466,7 @@
       </c>
       <c r="G545" s="19"/>
     </row>
-    <row r="546" s="9" customFormat="1" spans="1:7">
+    <row r="546" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A546" s="20" t="s">
         <v>1075</v>
       </c>
@@ -17480,7 +17483,7 @@
       </c>
       <c r="G546" s="19"/>
     </row>
-    <row r="547" s="9" customFormat="1" spans="1:7">
+    <row r="547" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A547" s="20" t="s">
         <v>1076</v>
       </c>
@@ -17497,7 +17500,7 @@
       </c>
       <c r="G547" s="19"/>
     </row>
-    <row r="548" s="9" customFormat="1" spans="1:7">
+    <row r="548" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A548" s="20" t="s">
         <v>1077</v>
       </c>
@@ -17514,7 +17517,7 @@
       </c>
       <c r="G548" s="19"/>
     </row>
-    <row r="549" s="9" customFormat="1" spans="1:7">
+    <row r="549" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A549" s="20" t="s">
         <v>1078</v>
       </c>
@@ -17531,7 +17534,7 @@
       </c>
       <c r="G549" s="19"/>
     </row>
-    <row r="550" s="9" customFormat="1" spans="1:7">
+    <row r="550" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A550" s="20" t="s">
         <v>1079</v>
       </c>
@@ -17550,7 +17553,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="551" s="9" customFormat="1" spans="1:7">
+    <row r="551" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A551" s="20" t="s">
         <v>1081</v>
       </c>
@@ -17567,7 +17570,7 @@
       </c>
       <c r="G551" s="19"/>
     </row>
-    <row r="552" s="9" customFormat="1" spans="1:7">
+    <row r="552" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A552" s="20" t="s">
         <v>1082</v>
       </c>
@@ -17584,7 +17587,7 @@
       </c>
       <c r="G552" s="19"/>
     </row>
-    <row r="553" s="9" customFormat="1" spans="1:7">
+    <row r="553" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A553" s="13" t="s">
         <v>1083</v>
       </c>
@@ -17603,7 +17606,7 @@
       </c>
       <c r="G553" s="1"/>
     </row>
-    <row r="554" s="9" customFormat="1" spans="1:7">
+    <row r="554" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A554" s="13" t="s">
         <v>1085</v>
       </c>
@@ -17624,7 +17627,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="555" s="9" customFormat="1" spans="1:7">
+    <row r="555" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A555" s="13" t="s">
         <v>1088</v>
       </c>
@@ -17645,7 +17648,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="556" s="9" customFormat="1" spans="1:7">
+    <row r="556" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A556" s="13" t="s">
         <v>1091</v>
       </c>
@@ -17666,7 +17669,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="557" s="9" customFormat="1" spans="1:7">
+    <row r="557" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A557" s="13" t="s">
         <v>1094</v>
       </c>
@@ -17687,7 +17690,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="558" s="9" customFormat="1" spans="1:7">
+    <row r="558" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A558" s="13" t="s">
         <v>1097</v>
       </c>
@@ -17706,7 +17709,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="559" s="9" customFormat="1" spans="1:7">
+    <row r="559" s="9" customFormat="1" ht="15.4" spans="1:7">
       <c r="A559" s="13" t="s">
         <v>1100</v>
       </c>
@@ -18295,7 +18298,7 @@
       </c>
       <c r="G587" s="14"/>
     </row>
-    <row r="588" ht="15.4" spans="1:7">
+    <row r="588" spans="1:7">
       <c r="A588" s="13" t="s">
         <v>1184</v>
       </c>
@@ -18312,7 +18315,7 @@
       </c>
       <c r="G588" s="14"/>
     </row>
-    <row r="589" s="8" customFormat="1" spans="1:7">
+    <row r="589" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A589" s="13" t="s">
         <v>1185</v>
       </c>
@@ -18350,7 +18353,7 @@
       </c>
       <c r="G590" s="14"/>
     </row>
-    <row r="591" s="8" customFormat="1" spans="1:7">
+    <row r="591" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A591" s="13" t="s">
         <v>1190</v>
       </c>
@@ -18388,7 +18391,7 @@
       </c>
       <c r="G592" s="14"/>
     </row>
-    <row r="593" s="8" customFormat="1" spans="1:7">
+    <row r="593" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A593" s="13" t="s">
         <v>1194</v>
       </c>
@@ -18426,7 +18429,7 @@
       </c>
       <c r="G594" s="14"/>
     </row>
-    <row r="595" s="8" customFormat="1" spans="1:7">
+    <row r="595" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A595" s="13" t="s">
         <v>1198</v>
       </c>
@@ -18466,7 +18469,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="597" s="8" customFormat="1" spans="1:7">
+    <row r="597" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A597" s="13" t="s">
         <v>1204</v>
       </c>
@@ -18504,7 +18507,7 @@
       </c>
       <c r="G598" s="14"/>
     </row>
-    <row r="599" s="8" customFormat="1" spans="1:7">
+    <row r="599" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A599" s="13" t="s">
         <v>1209</v>
       </c>
@@ -18563,7 +18566,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="602" s="8" customFormat="1" spans="1:7">
+    <row r="602" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A602" s="13" t="s">
         <v>1216</v>
       </c>
@@ -18582,7 +18585,7 @@
       </c>
       <c r="G602" s="14"/>
     </row>
-    <row r="603" s="8" customFormat="1" spans="1:7">
+    <row r="603" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A603" s="13" t="s">
         <v>1217</v>
       </c>
@@ -18620,7 +18623,7 @@
       </c>
       <c r="G604" s="14"/>
     </row>
-    <row r="605" s="8" customFormat="1" spans="1:7">
+    <row r="605" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A605" s="13" t="s">
         <v>1223</v>
       </c>
@@ -18639,7 +18642,7 @@
       </c>
       <c r="G605" s="14"/>
     </row>
-    <row r="606" s="8" customFormat="1" spans="1:7">
+    <row r="606" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A606" s="13" t="s">
         <v>1225</v>
       </c>
@@ -18658,7 +18661,7 @@
       </c>
       <c r="G606" s="14"/>
     </row>
-    <row r="607" s="8" customFormat="1" spans="1:7">
+    <row r="607" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A607" s="13" t="s">
         <v>1227</v>
       </c>
@@ -18677,7 +18680,7 @@
       </c>
       <c r="G607" s="14"/>
     </row>
-    <row r="608" s="8" customFormat="1" spans="1:7">
+    <row r="608" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A608" s="13" t="s">
         <v>1229</v>
       </c>
@@ -18696,7 +18699,7 @@
       </c>
       <c r="G608" s="14"/>
     </row>
-    <row r="609" s="8" customFormat="1" spans="1:7">
+    <row r="609" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A609" s="13" t="s">
         <v>1231</v>
       </c>
@@ -18717,7 +18720,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="610" s="8" customFormat="1" spans="1:7">
+    <row r="610" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A610" s="13" t="s">
         <v>1233</v>
       </c>
@@ -18736,7 +18739,7 @@
       </c>
       <c r="G610" s="14"/>
     </row>
-    <row r="611" s="8" customFormat="1" spans="1:7">
+    <row r="611" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A611" s="13" t="s">
         <v>1235</v>
       </c>
@@ -18759,7 +18762,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="612" s="8" customFormat="1" spans="1:7">
+    <row r="612" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A612" s="13" t="s">
         <v>1240</v>
       </c>
@@ -18778,7 +18781,7 @@
       </c>
       <c r="G612" s="14"/>
     </row>
-    <row r="613" s="8" customFormat="1" spans="1:7">
+    <row r="613" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A613" s="13" t="s">
         <v>1243</v>
       </c>
@@ -18797,7 +18800,7 @@
       </c>
       <c r="G613" s="14"/>
     </row>
-    <row r="614" s="8" customFormat="1" spans="1:7">
+    <row r="614" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A614" s="13" t="s">
         <v>1245</v>
       </c>
@@ -18816,7 +18819,7 @@
       </c>
       <c r="G614" s="14"/>
     </row>
-    <row r="615" s="8" customFormat="1" spans="1:7">
+    <row r="615" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A615" s="13" t="s">
         <v>1247</v>
       </c>
@@ -18835,7 +18838,7 @@
       </c>
       <c r="G615" s="14"/>
     </row>
-    <row r="616" s="8" customFormat="1" spans="1:7">
+    <row r="616" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A616" s="13" t="s">
         <v>1249</v>
       </c>
@@ -18852,7 +18855,7 @@
       </c>
       <c r="G616" s="14"/>
     </row>
-    <row r="617" s="8" customFormat="1" spans="1:7">
+    <row r="617" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A617" s="13" t="s">
         <v>1250</v>
       </c>
@@ -18871,7 +18874,7 @@
       </c>
       <c r="G617" s="14"/>
     </row>
-    <row r="618" s="8" customFormat="1" spans="1:7">
+    <row r="618" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A618" s="13" t="s">
         <v>1252</v>
       </c>
@@ -18890,7 +18893,7 @@
       </c>
       <c r="G618" s="14"/>
     </row>
-    <row r="619" s="8" customFormat="1" spans="1:7">
+    <row r="619" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A619" s="13" t="s">
         <v>1253</v>
       </c>
@@ -18911,7 +18914,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="620" s="8" customFormat="1" spans="1:7">
+    <row r="620" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A620" s="13" t="s">
         <v>1257</v>
       </c>
@@ -18930,7 +18933,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="621" s="8" customFormat="1" spans="1:7">
+    <row r="621" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A621" s="13" t="s">
         <v>1259</v>
       </c>
@@ -18949,7 +18952,7 @@
       </c>
       <c r="G621" s="14"/>
     </row>
-    <row r="622" s="8" customFormat="1" spans="1:7">
+    <row r="622" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A622" s="13" t="s">
         <v>1261</v>
       </c>
@@ -18968,7 +18971,7 @@
       </c>
       <c r="G622" s="14"/>
     </row>
-    <row r="623" s="8" customFormat="1" spans="1:7">
+    <row r="623" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A623" s="13" t="s">
         <v>1263</v>
       </c>
@@ -18987,7 +18990,7 @@
       </c>
       <c r="G623" s="14"/>
     </row>
-    <row r="624" s="8" customFormat="1" spans="1:7">
+    <row r="624" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A624" s="13" t="s">
         <v>1266</v>
       </c>
@@ -19006,7 +19009,7 @@
       </c>
       <c r="G624" s="14"/>
     </row>
-    <row r="625" s="8" customFormat="1" spans="1:7">
+    <row r="625" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A625" s="13" t="s">
         <v>1268</v>
       </c>
@@ -19023,7 +19026,7 @@
       </c>
       <c r="G625" s="14"/>
     </row>
-    <row r="626" s="8" customFormat="1" spans="1:7">
+    <row r="626" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A626" s="13" t="s">
         <v>1269</v>
       </c>
@@ -19042,7 +19045,7 @@
       </c>
       <c r="G626" s="14"/>
     </row>
-    <row r="627" s="8" customFormat="1" spans="1:7">
+    <row r="627" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A627" s="13" t="s">
         <v>1271</v>
       </c>
@@ -19061,7 +19064,7 @@
       </c>
       <c r="G627" s="14"/>
     </row>
-    <row r="628" s="8" customFormat="1" spans="1:7">
+    <row r="628" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A628" s="13" t="s">
         <v>1273</v>
       </c>
@@ -19080,7 +19083,7 @@
       </c>
       <c r="G628" s="14"/>
     </row>
-    <row r="629" s="8" customFormat="1" spans="1:7">
+    <row r="629" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A629" s="13" t="s">
         <v>1275</v>
       </c>
@@ -19099,7 +19102,7 @@
       </c>
       <c r="G629" s="14"/>
     </row>
-    <row r="630" s="8" customFormat="1" spans="1:7">
+    <row r="630" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A630" s="13" t="s">
         <v>1278</v>
       </c>
@@ -19118,7 +19121,7 @@
       </c>
       <c r="G630" s="14"/>
     </row>
-    <row r="631" s="8" customFormat="1" spans="1:7">
+    <row r="631" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A631" s="13" t="s">
         <v>1280</v>
       </c>
@@ -19137,7 +19140,7 @@
       </c>
       <c r="G631" s="14"/>
     </row>
-    <row r="632" s="8" customFormat="1" spans="1:7">
+    <row r="632" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A632" s="13" t="s">
         <v>1283</v>
       </c>
@@ -19158,7 +19161,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="633" s="8" customFormat="1" spans="1:7">
+    <row r="633" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A633" s="13" t="s">
         <v>1287</v>
       </c>
@@ -19179,7 +19182,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="634" s="8" customFormat="1" spans="1:7">
+    <row r="634" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A634" s="13" t="s">
         <v>1291</v>
       </c>
@@ -19200,7 +19203,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="635" s="8" customFormat="1" spans="1:7">
+    <row r="635" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A635" s="13" t="s">
         <v>1295</v>
       </c>
@@ -19221,7 +19224,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="636" s="8" customFormat="1" spans="1:7">
+    <row r="636" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A636" s="13" t="s">
         <v>1298</v>
       </c>
@@ -19242,7 +19245,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="637" s="8" customFormat="1" spans="1:7">
+    <row r="637" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A637" s="13" t="s">
         <v>1301</v>
       </c>
@@ -19261,7 +19264,7 @@
       </c>
       <c r="G637" s="14"/>
     </row>
-    <row r="638" s="8" customFormat="1" spans="1:7">
+    <row r="638" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A638" s="13" t="s">
         <v>1304</v>
       </c>
@@ -19282,7 +19285,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="639" s="8" customFormat="1" spans="1:7">
+    <row r="639" s="8" customFormat="1" ht="15.45" spans="1:7">
       <c r="A639" s="13" t="s">
         <v>1308</v>
       </c>
@@ -19305,7 +19308,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="640" s="8" customFormat="1" spans="1:7">
+    <row r="640" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A640" s="13" t="s">
         <v>1312</v>
       </c>
@@ -19326,7 +19329,7 @@
       </c>
       <c r="G640" s="14"/>
     </row>
-    <row r="641" s="8" customFormat="1" spans="1:7">
+    <row r="641" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A641" s="13" t="s">
         <v>1315</v>
       </c>
@@ -19347,7 +19350,7 @@
       </c>
       <c r="G641" s="14"/>
     </row>
-    <row r="642" s="8" customFormat="1" spans="1:7">
+    <row r="642" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A642" s="13" t="s">
         <v>1318</v>
       </c>
@@ -19370,7 +19373,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="643" s="8" customFormat="1" spans="1:7">
+    <row r="643" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A643" s="13" t="s">
         <v>1322</v>
       </c>
@@ -19391,7 +19394,7 @@
       </c>
       <c r="G643" s="14"/>
     </row>
-    <row r="644" s="8" customFormat="1" spans="1:7">
+    <row r="644" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A644" s="13" t="s">
         <v>1325</v>
       </c>
@@ -19412,7 +19415,7 @@
       </c>
       <c r="G644" s="14"/>
     </row>
-    <row r="645" s="8" customFormat="1" spans="1:7">
+    <row r="645" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A645" s="13" t="s">
         <v>1328</v>
       </c>
@@ -19433,7 +19436,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="646" s="8" customFormat="1" spans="1:7">
+    <row r="646" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A646" s="13" t="s">
         <v>1332</v>
       </c>
@@ -19454,7 +19457,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="647" s="8" customFormat="1" spans="1:7">
+    <row r="647" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A647" s="13" t="s">
         <v>1335</v>
       </c>
@@ -19473,7 +19476,7 @@
       </c>
       <c r="G647" s="14"/>
     </row>
-    <row r="648" s="8" customFormat="1" spans="1:7">
+    <row r="648" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A648" s="13" t="s">
         <v>1337</v>
       </c>
@@ -19494,7 +19497,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="649" s="8" customFormat="1" spans="1:7">
+    <row r="649" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A649" s="13" t="s">
         <v>1340</v>
       </c>
@@ -19513,7 +19516,7 @@
       </c>
       <c r="G649" s="14"/>
     </row>
-    <row r="650" s="8" customFormat="1" spans="1:7">
+    <row r="650" s="8" customFormat="1" ht="15.45" spans="1:7">
       <c r="A650" s="13" t="s">
         <v>1342</v>
       </c>
@@ -19532,7 +19535,7 @@
       </c>
       <c r="G650" s="14"/>
     </row>
-    <row r="651" s="8" customFormat="1" spans="1:7">
+    <row r="651" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A651" s="13" t="s">
         <v>1344</v>
       </c>
@@ -19553,7 +19556,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="652" s="8" customFormat="1" spans="1:7">
+    <row r="652" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A652" s="13" t="s">
         <v>1348</v>
       </c>
@@ -19574,7 +19577,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="653" s="8" customFormat="1" spans="1:7">
+    <row r="653" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A653" s="13" t="s">
         <v>1351</v>
       </c>
@@ -19593,7 +19596,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="654" s="8" customFormat="1" spans="1:7">
+    <row r="654" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A654" s="13" t="s">
         <v>1354</v>
       </c>
@@ -19623,38 +19626,38 @@
         <v>355</v>
       </c>
       <c r="D655" s="13" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="E655" s="14" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F655" s="14" t="s">
         <v>1359</v>
       </c>
-      <c r="F655" s="14" t="s">
-        <v>1356</v>
-      </c>
-      <c r="G655" s="14"/>
-    </row>
-    <row r="656" s="8" customFormat="1" spans="1:7">
+      <c r="G655" s="8" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="656" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A656" s="13" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B656" s="14"/>
       <c r="C656" s="13" t="s">
         <v>355</v>
       </c>
       <c r="D656" s="13" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="E656" s="14" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F656" s="14" t="s">
         <v>1356</v>
       </c>
-      <c r="G656" s="18" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="657" s="8" customFormat="1" spans="1:7">
+      <c r="G656" s="14"/>
+    </row>
+    <row r="657" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A657" s="13" t="s">
         <v>1363</v>
       </c>
@@ -19663,17 +19666,19 @@
         <v>355</v>
       </c>
       <c r="D657" s="13" t="s">
-        <v>165</v>
+        <v>205</v>
       </c>
       <c r="E657" s="14" t="s">
         <v>1364</v>
       </c>
       <c r="F657" s="14" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G657" s="18" t="s">
         <v>1365</v>
       </c>
-      <c r="G657" s="14"/>
-    </row>
-    <row r="658" s="8" customFormat="1" spans="1:7">
+    </row>
+    <row r="658" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A658" s="13" t="s">
         <v>1366</v>
       </c>
@@ -19682,57 +19687,57 @@
         <v>355</v>
       </c>
       <c r="D658" s="13" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E658" s="14" t="s">
         <v>1367</v>
       </c>
       <c r="F658" s="14" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="G658" s="14"/>
     </row>
-    <row r="659" s="8" customFormat="1" spans="1:7">
+    <row r="659" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A659" s="13" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B659" s="14"/>
       <c r="C659" s="13" t="s">
         <v>355</v>
       </c>
       <c r="D659" s="13" t="s">
-        <v>265</v>
+        <v>159</v>
       </c>
       <c r="E659" s="14" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="F659" s="14" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G659" s="18" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G659" s="14"/>
+    </row>
+    <row r="660" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A660" s="13" t="s">
         <v>1371</v>
-      </c>
-    </row>
-    <row r="660" s="8" customFormat="1" spans="1:7">
-      <c r="A660" s="13" t="s">
-        <v>1372</v>
       </c>
       <c r="B660" s="14"/>
       <c r="C660" s="13" t="s">
-        <v>801</v>
+        <v>355</v>
       </c>
       <c r="D660" s="13" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="E660" s="14" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F660" s="14" t="s">
         <v>1373</v>
       </c>
-      <c r="F660" s="14" t="s">
+      <c r="G660" s="18" t="s">
         <v>1374</v>
       </c>
-      <c r="G660" s="14"/>
-    </row>
-    <row r="661" s="8" customFormat="1" spans="1:7">
+    </row>
+    <row r="661" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A661" s="13" t="s">
         <v>1375</v>
       </c>
@@ -19741,7 +19746,7 @@
         <v>801</v>
       </c>
       <c r="D661" s="13" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E661" s="14" t="s">
         <v>1376</v>
@@ -19751,7 +19756,7 @@
       </c>
       <c r="G661" s="14"/>
     </row>
-    <row r="662" s="8" customFormat="1" spans="1:7">
+    <row r="662" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A662" s="13" t="s">
         <v>1378</v>
       </c>
@@ -19760,7 +19765,7 @@
         <v>801</v>
       </c>
       <c r="D662" s="13" t="s">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="E662" s="14" t="s">
         <v>1379</v>
@@ -19770,7 +19775,7 @@
       </c>
       <c r="G662" s="14"/>
     </row>
-    <row r="663" s="8" customFormat="1" spans="1:7">
+    <row r="663" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A663" s="13" t="s">
         <v>1381</v>
       </c>
@@ -19789,7 +19794,7 @@
       </c>
       <c r="G663" s="14"/>
     </row>
-    <row r="664" s="8" customFormat="1" spans="1:7">
+    <row r="664" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A664" s="13" t="s">
         <v>1384</v>
       </c>
@@ -19798,168 +19803,170 @@
         <v>801</v>
       </c>
       <c r="D664" s="13" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E664" s="14" t="s">
         <v>1385</v>
       </c>
-      <c r="F664" s="14"/>
+      <c r="F664" s="14" t="s">
+        <v>1386</v>
+      </c>
       <c r="G664" s="14"/>
     </row>
-    <row r="665" s="8" customFormat="1" spans="1:7">
+    <row r="665" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A665" s="13" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B665" s="14"/>
       <c r="C665" s="13" t="s">
-        <v>736</v>
+        <v>801</v>
       </c>
       <c r="D665" s="13" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E665" s="14" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="F665" s="14"/>
       <c r="G665" s="14"/>
     </row>
-    <row r="666" s="8" customFormat="1" spans="1:7">
+    <row r="666" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A666" s="13" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B666" s="14"/>
       <c r="C666" s="13" t="s">
-        <v>1389</v>
+        <v>736</v>
       </c>
       <c r="D666" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="E666" s="14"/>
-      <c r="F666" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E666" s="14" t="s">
         <v>1390</v>
       </c>
+      <c r="F666" s="14"/>
       <c r="G666" s="14"/>
     </row>
-    <row r="667" s="8" customFormat="1" spans="1:7">
+    <row r="667" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A667" s="13" t="s">
         <v>1391</v>
       </c>
       <c r="B667" s="14"/>
       <c r="C667" s="13" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="D667" s="13" t="s">
-        <v>265</v>
+        <v>159</v>
       </c>
       <c r="E667" s="14"/>
       <c r="F667" s="14" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="G667" s="14"/>
     </row>
-    <row r="668" s="8" customFormat="1" spans="1:7">
+    <row r="668" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A668" s="13" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B668" s="14"/>
       <c r="C668" s="13" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="D668" s="13" t="s">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="E668" s="14"/>
       <c r="F668" s="14" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="G668" s="14"/>
     </row>
-    <row r="669" s="8" customFormat="1" spans="1:7">
+    <row r="669" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A669" s="13" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B669" s="14"/>
       <c r="C669" s="13" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="D669" s="13" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E669" s="14"/>
       <c r="F669" s="14" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="G669" s="14"/>
     </row>
-    <row r="670" s="8" customFormat="1" spans="1:7">
+    <row r="670" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A670" s="13" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B670" s="14"/>
       <c r="C670" s="13" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="D670" s="13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E670" s="14"/>
       <c r="F670" s="14" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="G670" s="14"/>
     </row>
-    <row r="671" s="8" customFormat="1" spans="1:7">
+    <row r="671" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A671" s="13" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B671" s="14"/>
       <c r="C671" s="13" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="D671" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E671" s="14"/>
       <c r="F671" s="14" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="G671" s="14"/>
     </row>
-    <row r="672" s="8" customFormat="1" spans="1:7">
+    <row r="672" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A672" s="13" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B672" s="14"/>
       <c r="C672" s="13" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="D672" s="13" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E672" s="14"/>
       <c r="F672" s="14" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="G672" s="14"/>
     </row>
-    <row r="673" s="8" customFormat="1" spans="1:7">
+    <row r="673" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A673" s="13" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B673" s="14" t="s">
         <v>1404</v>
       </c>
-      <c r="C673" s="13"/>
+      <c r="B673" s="14"/>
+      <c r="C673" s="13" t="s">
+        <v>1392</v>
+      </c>
       <c r="D673" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="E673" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E673" s="14"/>
+      <c r="F673" s="14" t="s">
         <v>1405</v>
       </c>
-      <c r="F673" s="14"/>
       <c r="G673" s="14"/>
     </row>
-    <row r="674" s="8" customFormat="1" spans="1:7">
+    <row r="674" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A674" s="13" t="s">
         <v>1406</v>
       </c>
@@ -19968,101 +19975,99 @@
       </c>
       <c r="C674" s="13"/>
       <c r="D674" s="13" t="s">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="E674" s="14" t="s">
         <v>1408</v>
       </c>
-      <c r="F674" s="14" t="s">
+      <c r="F674" s="14"/>
+      <c r="G674" s="14"/>
+    </row>
+    <row r="675" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A675" s="13" t="s">
         <v>1409</v>
       </c>
-      <c r="G674" s="14"/>
-    </row>
-    <row r="675" s="8" customFormat="1" spans="1:7">
-      <c r="A675" s="13" t="s">
+      <c r="B675" s="14" t="s">
         <v>1410</v>
       </c>
-      <c r="B675" s="14" t="s">
+      <c r="C675" s="13"/>
+      <c r="D675" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E675" s="14" t="s">
         <v>1411</v>
       </c>
-      <c r="C675" s="13" t="s">
+      <c r="F675" s="14" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G675" s="14"/>
+    </row>
+    <row r="676" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A676" s="13" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B676" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C676" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D675" s="13" t="s">
+      <c r="D676" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="E675" s="14" t="s">
-        <v>1412</v>
-      </c>
-      <c r="F675" s="14" t="s">
-        <v>1413</v>
-      </c>
-      <c r="G675" s="14" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="676" s="8" customFormat="1" spans="1:7">
-      <c r="A676" s="13" t="s">
+      <c r="E676" s="14" t="s">
         <v>1415</v>
       </c>
-      <c r="B676" s="14" t="s">
+      <c r="F676" s="14" t="s">
         <v>1416</v>
       </c>
-      <c r="C676" s="13"/>
-      <c r="D676" s="13" t="s">
+      <c r="G676" s="14" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="677" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A677" s="13" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B677" s="14" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C677" s="13"/>
+      <c r="D677" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E676" s="14" t="s">
-        <v>1417</v>
-      </c>
-      <c r="F676" s="14" t="s">
-        <v>1418</v>
-      </c>
-      <c r="G676" s="14" t="s">
-        <v>1419</v>
-      </c>
-    </row>
-    <row r="677" s="8" customFormat="1" spans="1:7">
-      <c r="A677" s="17" t="s">
+      <c r="E677" s="14" t="s">
         <v>1420</v>
       </c>
-      <c r="B677" s="26" t="s">
+      <c r="F677" s="14" t="s">
         <v>1421</v>
       </c>
-      <c r="C677" s="13" t="s">
+      <c r="G677" s="14" t="s">
         <v>1422</v>
       </c>
-      <c r="D677" s="13"/>
-      <c r="E677" s="14" t="s">
+    </row>
+    <row r="678" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A678" s="17" t="s">
         <v>1423</v>
       </c>
-      <c r="F677" s="14" t="s">
+      <c r="B678" s="26" t="s">
         <v>1424</v>
       </c>
-      <c r="G677" s="14" t="s">
+      <c r="C678" s="13" t="s">
         <v>1425</v>
       </c>
-    </row>
-    <row r="678" s="8" customFormat="1" spans="1:7">
-      <c r="A678" s="13" t="s">
+      <c r="D678" s="13"/>
+      <c r="E678" s="14" t="s">
         <v>1426</v>
       </c>
-      <c r="B678" s="14" t="s">
+      <c r="F678" s="14" t="s">
         <v>1427</v>
       </c>
-      <c r="C678" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="D678" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E678" s="14"/>
-      <c r="F678" s="1" t="s">
+      <c r="G678" s="14" t="s">
         <v>1428</v>
       </c>
-      <c r="G678" s="14"/>
-    </row>
-    <row r="679" s="8" customFormat="1" spans="1:7">
+    </row>
+    <row r="679" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A679" s="13" t="s">
         <v>1429</v>
       </c>
@@ -20073,123 +20078,129 @@
         <v>379</v>
       </c>
       <c r="D679" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="E679" s="14"/>
+      <c r="F679" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G679" s="14"/>
+    </row>
+    <row r="680" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A680" s="13" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B680" s="14" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C680" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="D680" s="13" t="s">
         <v>142</v>
-      </c>
-      <c r="E679" s="14"/>
-      <c r="F679" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="G679" s="14"/>
-    </row>
-    <row r="680" s="8" customFormat="1" spans="1:7">
-      <c r="A680" s="13" t="s">
-        <v>1431</v>
-      </c>
-      <c r="B680" s="14"/>
-      <c r="C680" s="13" t="s">
-        <v>1389</v>
-      </c>
-      <c r="D680" s="13" t="s">
-        <v>159</v>
       </c>
       <c r="E680" s="14"/>
       <c r="F680" s="14" t="s">
-        <v>1396</v>
+        <v>219</v>
       </c>
       <c r="G680" s="14"/>
     </row>
-    <row r="681" s="8" customFormat="1" spans="1:7">
-      <c r="A681" s="17" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B681" s="26" t="s">
-        <v>1433</v>
-      </c>
-      <c r="C681" s="13"/>
+    <row r="681" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A681" s="13" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B681" s="14"/>
+      <c r="C681" s="13" t="s">
+        <v>1392</v>
+      </c>
       <c r="D681" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E681" s="14"/>
+      <c r="F681" s="14" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G681" s="14"/>
+    </row>
+    <row r="682" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A682" s="17" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B682" s="26" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C682" s="13"/>
+      <c r="D682" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E681" s="14" t="s">
-        <v>1434</v>
-      </c>
-      <c r="F681" s="14"/>
-      <c r="G681" s="14"/>
-    </row>
-    <row r="682" s="8" customFormat="1" spans="1:7">
-      <c r="A682" s="13" t="s">
-        <v>1435</v>
-      </c>
-      <c r="B682" s="14" t="s">
-        <v>1436</v>
-      </c>
-      <c r="C682" s="13" t="s">
+      <c r="E682" s="14" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F682" s="14"/>
+      <c r="G682" s="14"/>
+    </row>
+    <row r="683" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A683" s="13" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B683" s="14" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C683" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="D682" s="13" t="s">
-        <v>1437</v>
-      </c>
-      <c r="E682" s="14"/>
-      <c r="F682" s="14" t="s">
-        <v>1438</v>
-      </c>
-      <c r="G682" s="14" t="s">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="683" s="8" customFormat="1" spans="1:7">
-      <c r="A683" s="13" t="s">
+      <c r="D683" s="13" t="s">
         <v>1440</v>
       </c>
-      <c r="B683" s="14" t="s">
+      <c r="E683" s="14"/>
+      <c r="F683" s="14" t="s">
         <v>1441</v>
       </c>
-      <c r="C683" s="13" t="s">
+      <c r="G683" s="14" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="684" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A684" s="13" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B684" s="14" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C684" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="D683" s="13" t="s">
+      <c r="D684" s="13" t="s">
         <v>265</v>
       </c>
-      <c r="E683" s="14"/>
-      <c r="F683" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="G683" s="14"/>
-    </row>
-    <row r="684" s="8" customFormat="1" spans="1:7">
-      <c r="A684" s="13" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B684" s="14" t="s">
+      <c r="E684" s="14"/>
+      <c r="F684" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G684" s="14"/>
+    </row>
+    <row r="685" s="8" customFormat="1" ht="15.4" spans="1:7">
+      <c r="A685" s="13" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B685" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="C684" s="13"/>
-      <c r="D684" s="13" t="s">
+      <c r="C685" s="13"/>
+      <c r="D685" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="E684" s="14"/>
-      <c r="F684" s="14"/>
-      <c r="G684" s="14"/>
-    </row>
-    <row r="685" s="8" customFormat="1" spans="1:7">
-      <c r="A685" s="13" t="s">
-        <v>1443</v>
-      </c>
-      <c r="B685" s="14" t="s">
-        <v>1444</v>
-      </c>
-      <c r="C685" s="13"/>
-      <c r="D685" s="13"/>
       <c r="E685" s="14"/>
       <c r="F685" s="14" t="s">
         <v>219</v>
       </c>
       <c r="G685" s="14" t="s">
-        <v>1445</v>
-      </c>
-    </row>
-    <row r="686" s="8" customFormat="1" spans="1:7">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="686" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A686" s="13" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B686" s="14" t="s">
         <v>412</v>
@@ -20199,12 +20210,16 @@
         <v>265</v>
       </c>
       <c r="E686" s="14"/>
-      <c r="F686" s="14"/>
-      <c r="G686" s="14"/>
-    </row>
-    <row r="687" s="8" customFormat="1" spans="1:7">
+      <c r="F686" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G686" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="687" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A687" s="13" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B687" s="14" t="s">
         <v>418</v>
@@ -20214,42 +20229,54 @@
         <v>265</v>
       </c>
       <c r="E687" s="14"/>
-      <c r="F687" s="14"/>
-      <c r="G687" s="14"/>
-    </row>
-    <row r="688" s="8" customFormat="1" spans="1:7">
+      <c r="F687" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G687" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="688" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A688" s="13" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B688" s="14" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="C688" s="13"/>
       <c r="D688" s="13" t="s">
         <v>152</v>
       </c>
       <c r="E688" s="14"/>
-      <c r="F688" s="14"/>
-      <c r="G688" s="14"/>
-    </row>
-    <row r="689" s="8" customFormat="1" spans="1:7">
+      <c r="F688" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G688" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="689" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A689" s="13" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B689" s="14" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C689" s="13"/>
       <c r="D689" s="13" t="s">
         <v>165</v>
       </c>
       <c r="E689" s="14"/>
-      <c r="F689" s="14"/>
-      <c r="G689" s="14"/>
-    </row>
-    <row r="690" s="8" customFormat="1" spans="1:7">
+      <c r="F689" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G689" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="690" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A690" s="13" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B690" s="14" t="s">
         <v>420</v>
@@ -20259,45 +20286,57 @@
         <v>142</v>
       </c>
       <c r="E690" s="14"/>
-      <c r="F690" s="14"/>
-      <c r="G690" s="14"/>
-    </row>
-    <row r="691" s="8" customFormat="1" spans="1:7">
+      <c r="F690" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G690" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="691" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A691" s="13" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B691" s="14" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C691" s="13"/>
       <c r="D691" s="13" t="s">
         <v>265</v>
       </c>
       <c r="E691" s="14"/>
-      <c r="F691" s="14"/>
-      <c r="G691" s="14"/>
-    </row>
-    <row r="692" s="8" customFormat="1" spans="1:7">
+      <c r="F691" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G691" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="692" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A692" s="13" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B692" s="14" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="C692" s="13"/>
       <c r="D692" s="13" t="s">
         <v>162</v>
       </c>
       <c r="E692" s="14"/>
-      <c r="F692" s="14"/>
-      <c r="G692" s="14"/>
-    </row>
-    <row r="693" s="8" customFormat="1" spans="1:7">
+      <c r="F692" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G692" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="693" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A693" s="13" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B693" s="14" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="C693" s="13"/>
       <c r="D693" s="13" t="s">
@@ -20307,101 +20346,127 @@
       <c r="F693" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="G693" s="14"/>
-    </row>
-    <row r="694" s="8" customFormat="1" spans="1:7">
+      <c r="G693" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="694" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A694" s="13" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B694" s="14" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C694" s="13"/>
       <c r="D694" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E694" s="14"/>
-      <c r="F694" s="14"/>
-      <c r="G694" s="14"/>
-    </row>
-    <row r="695" s="8" customFormat="1" spans="1:7">
+      <c r="F694" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G694" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="695" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A695" s="13" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B695" s="14" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C695" s="13"/>
       <c r="D695" s="13" t="s">
         <v>159</v>
       </c>
       <c r="E695" s="14"/>
-      <c r="F695" s="14"/>
-      <c r="G695" s="14"/>
-    </row>
-    <row r="696" s="8" customFormat="1" spans="1:7">
+      <c r="F695" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G695" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="696" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A696" s="13" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B696" s="14" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="C696" s="13"/>
       <c r="D696" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E696" s="14"/>
-      <c r="F696" s="14"/>
-      <c r="G696" s="14"/>
-    </row>
-    <row r="697" s="8" customFormat="1" spans="1:7">
+      <c r="F696" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G696" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="697" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A697" s="13" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B697" s="14" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="C697" s="13"/>
       <c r="D697" s="13" t="s">
         <v>290</v>
       </c>
       <c r="E697" s="14"/>
-      <c r="F697" s="14"/>
-      <c r="G697" s="14"/>
-    </row>
-    <row r="698" s="8" customFormat="1" spans="1:7">
+      <c r="F697" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G697" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="698" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A698" s="13" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B698" s="14" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C698" s="13"/>
       <c r="D698" s="13" t="s">
         <v>165</v>
       </c>
       <c r="E698" s="14"/>
-      <c r="F698" s="14"/>
-      <c r="G698" s="14"/>
-    </row>
-    <row r="699" s="8" customFormat="1" spans="1:7">
+      <c r="F698" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G698" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="699" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A699" s="13" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B699" s="14" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C699" s="13"/>
       <c r="D699" s="13" t="s">
         <v>225</v>
       </c>
       <c r="E699" s="14"/>
-      <c r="F699" s="14"/>
-      <c r="G699" s="14"/>
-    </row>
-    <row r="700" s="8" customFormat="1" spans="1:7">
+      <c r="F699" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G699" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="700" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A700" s="13" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B700" s="14" t="s">
         <v>402</v>
@@ -20411,177 +20476,225 @@
         <v>165</v>
       </c>
       <c r="E700" s="14"/>
-      <c r="F700" s="14"/>
-      <c r="G700" s="14"/>
-    </row>
-    <row r="701" s="8" customFormat="1" spans="1:7">
+      <c r="F700" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G700" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="701" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A701" s="13" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B701" s="14" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="C701" s="13"/>
       <c r="D701" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E701" s="14"/>
-      <c r="F701" s="14"/>
-      <c r="G701" s="14"/>
-    </row>
-    <row r="702" s="8" customFormat="1" spans="1:7">
+      <c r="F701" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G701" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="702" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A702" s="13" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B702" s="14" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C702" s="13"/>
       <c r="D702" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E702" s="14"/>
-      <c r="F702" s="14"/>
-      <c r="G702" s="14"/>
-    </row>
-    <row r="703" s="8" customFormat="1" spans="1:7">
+      <c r="F702" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G702" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="703" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A703" s="13" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B703" s="14" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C703" s="13"/>
       <c r="D703" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E703" s="14"/>
-      <c r="F703" s="14"/>
-      <c r="G703" s="14"/>
-    </row>
-    <row r="704" s="8" customFormat="1" spans="1:7">
+      <c r="F703" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G703" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="704" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A704" s="13" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B704" s="14" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C704" s="13"/>
       <c r="D704" s="13" t="s">
         <v>265</v>
       </c>
       <c r="E704" s="14"/>
-      <c r="F704" s="14"/>
-      <c r="G704" s="14"/>
-    </row>
-    <row r="705" s="8" customFormat="1" spans="1:7">
+      <c r="F704" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G704" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="705" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A705" s="13" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B705" s="14" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="C705" s="13"/>
       <c r="D705" s="13" t="s">
         <v>142</v>
       </c>
       <c r="E705" s="14"/>
-      <c r="F705" s="14"/>
-      <c r="G705" s="14"/>
-    </row>
-    <row r="706" s="8" customFormat="1" spans="1:7">
+      <c r="F705" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G705" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="706" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A706" s="13" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B706" s="14" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="C706" s="13"/>
       <c r="D706" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E706" s="14"/>
-      <c r="F706" s="14"/>
-      <c r="G706" s="14"/>
-    </row>
-    <row r="707" s="8" customFormat="1" spans="1:7">
+      <c r="F706" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G706" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="707" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A707" s="13" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B707" s="14" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C707" s="13"/>
       <c r="D707" s="13" t="s">
         <v>142</v>
       </c>
       <c r="E707" s="14"/>
-      <c r="F707" s="14"/>
-      <c r="G707" s="14"/>
-    </row>
-    <row r="708" s="8" customFormat="1" spans="1:7">
+      <c r="F707" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G707" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="708" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A708" s="13" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B708" s="14" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="C708" s="13"/>
       <c r="D708" s="13" t="s">
         <v>139</v>
       </c>
       <c r="E708" s="14"/>
-      <c r="F708" s="14"/>
-      <c r="G708" s="14"/>
-    </row>
-    <row r="709" s="8" customFormat="1" spans="1:7">
+      <c r="F708" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G708" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="709" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A709" s="13" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B709" s="14" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C709" s="13"/>
       <c r="D709" s="13" t="s">
         <v>243</v>
       </c>
       <c r="E709" s="14"/>
-      <c r="F709" s="14"/>
-      <c r="G709" s="14"/>
-    </row>
-    <row r="710" s="8" customFormat="1" spans="1:7">
+      <c r="F709" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G709" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="710" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A710" s="13" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B710" s="14" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="C710" s="13"/>
       <c r="D710" s="13" t="s">
         <v>159</v>
       </c>
       <c r="E710" s="14"/>
-      <c r="F710" s="14"/>
-      <c r="G710" s="14"/>
-    </row>
-    <row r="711" s="8" customFormat="1" spans="1:7">
+      <c r="F710" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G710" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="711" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A711" s="13" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B711" s="14" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C711" s="13"/>
       <c r="D711" s="13" t="s">
         <v>155</v>
       </c>
       <c r="E711" s="14"/>
-      <c r="F711" s="14"/>
-      <c r="G711" s="14"/>
-    </row>
-    <row r="712" s="8" customFormat="1" spans="1:7">
+      <c r="F711" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G711" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="712" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A712" s="13" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B712" s="14" t="s">
         <v>475</v>
@@ -20591,42 +20704,54 @@
         <v>290</v>
       </c>
       <c r="E712" s="14"/>
-      <c r="F712" s="14"/>
-      <c r="G712" s="14"/>
-    </row>
-    <row r="713" s="8" customFormat="1" spans="1:7">
+      <c r="F712" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G712" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="713" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A713" s="13" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B713" s="14" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="C713" s="13"/>
       <c r="D713" s="13" t="s">
         <v>162</v>
       </c>
       <c r="E713" s="14"/>
-      <c r="F713" s="14"/>
-      <c r="G713" s="14"/>
-    </row>
-    <row r="714" s="8" customFormat="1" spans="1:7">
+      <c r="F713" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G713" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="714" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A714" s="13" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B714" s="14" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="C714" s="13"/>
       <c r="D714" s="13" t="s">
         <v>265</v>
       </c>
       <c r="E714" s="14"/>
-      <c r="F714" s="14"/>
-      <c r="G714" s="14"/>
-    </row>
-    <row r="715" s="8" customFormat="1" spans="1:7">
+      <c r="F714" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G714" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="715" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A715" s="13" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B715" s="14" t="s">
         <v>700</v>
@@ -20636,12 +20761,16 @@
         <v>225</v>
       </c>
       <c r="E715" s="14"/>
-      <c r="F715" s="14"/>
-      <c r="G715" s="14"/>
-    </row>
-    <row r="716" s="8" customFormat="1" spans="1:7">
+      <c r="F715" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G715" s="14" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="716" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A716" s="13" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B716" s="14"/>
       <c r="C716" s="13" t="s">
@@ -20655,63 +20784,63 @@
         <v>219</v>
       </c>
       <c r="G716" s="14" t="s">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="717" s="8" customFormat="1" spans="1:7">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="717" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A717" s="13" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B717" s="14" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C717" s="13"/>
       <c r="D717" s="13"/>
       <c r="E717" s="14"/>
       <c r="F717" s="1" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="G717" s="14" t="s">
-        <v>1504</v>
-      </c>
-    </row>
-    <row r="718" s="8" customFormat="1" spans="1:7">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="718" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A718" s="13" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B718" s="14" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C718" s="13"/>
       <c r="D718" s="13"/>
       <c r="E718" s="14"/>
       <c r="F718" s="1" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="G718" s="14" t="s">
-        <v>1507</v>
-      </c>
-    </row>
-    <row r="719" s="8" customFormat="1" spans="1:7">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="719" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A719" s="13" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B719" s="14" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="C719" s="13"/>
       <c r="D719" s="13"/>
       <c r="E719" s="14"/>
       <c r="F719" s="1" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="G719" s="14" t="s">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="720" s="8" customFormat="1" spans="1:7">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="720" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A720" s="13" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B720" s="14" t="s">
         <v>704</v>
@@ -20720,48 +20849,50 @@
       <c r="D720" s="13"/>
       <c r="E720" s="14"/>
       <c r="F720" s="1" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="G720" s="14" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="721" s="8" customFormat="1" spans="1:7">
       <c r="A721" s="13" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B721" s="14" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C721" s="13"/>
       <c r="D721" s="13"/>
+      <c r="E721" s="8"/>
       <c r="F721" s="14" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="G721" s="14"/>
     </row>
     <row r="722" s="8" customFormat="1" spans="1:7">
       <c r="A722" s="13" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B722" s="14" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C722" s="13"/>
       <c r="D722" s="13"/>
+      <c r="E722" s="8"/>
       <c r="F722" s="14" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="G722" s="14" t="s">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="723" s="8" customFormat="1" spans="1:7">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="723" s="8" customFormat="1" ht="15.4" spans="1:7">
       <c r="A723" s="13" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B723" s="14" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C723" s="13"/>
       <c r="D723" s="13" t="s">
@@ -20772,14 +20903,11 @@
         <v>219</v>
       </c>
       <c r="G723" s="14" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G588" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:G588">
-      <sortCondition ref="A1"/>
-    </sortState>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G723" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A1:A571 A580:A1048576">

--- a/xlsx/BWV.xlsx
+++ b/xlsx/BWV.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9805"/>
+    <workbookView windowWidth="21942" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="BWV" sheetId="1" r:id="rId1"/>
@@ -7799,7 +7799,7 @@
     <t>BWV 912a</t>
   </si>
   <si>
-    <t>Variations sur un mouvement de la Toccata BWV 912</t>
+    <t>Variations on a movement of the Toccata BWV 912</t>
   </si>
   <si>
     <t>BWV 913</t>
@@ -7820,7 +7820,7 @@
     <t>BWV 918</t>
   </si>
   <si>
-    <t>Fantaisie sur un Rondo</t>
+    <t>Fantaisie on a Rondo</t>
   </si>
   <si>
     <t>BWV 919</t>
@@ -8469,7 +8469,7 @@
 4. Presto</t>
   </si>
   <si>
-    <t>Solo Violin solo</t>
+    <t>Solo Violin</t>
   </si>
   <si>
     <t>BWV 1002</t>

--- a/xlsx/BWV.xlsx
+++ b/xlsx/BWV.xlsx
@@ -39186,7 +39186,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I1225" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:I1225">
+    <sortState ref="A1:I1225">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
